--- a/strategy/finmodel-wif.xlsx
+++ b/strategy/finmodel-wif.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="97">
   <si>
     <t xml:space="preserve">Рычаги финмодели WIF</t>
   </si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Модель по месяцам · базовый сценарий</t>
   </si>
   <si>
-    <t xml:space="preserve">Синие строки — вводные: траектория клиентов и план расхода. Всё остальное — формулы. Траектория проведена через контрольные точки target-state-18m.md (мес. 6, 12, 15, 18), между ними экспонента.</t>
+    <t xml:space="preserve">Синие строки — вводные: поток новых клиентов (план продаж), визиты, штат, расход. Всё остальное — формулы: база = прошлый месяц × (1 − отток) + новые. Поменяй поток или отток — пересчитается выручка, касса и проверки.</t>
   </si>
   <si>
     <t xml:space="preserve">Месяц</t>
@@ -147,15 +147,15 @@
     <t xml:space="preserve">Единица</t>
   </si>
   <si>
+    <t xml:space="preserve">Новых компаний за месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">шт.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Активных компаний</t>
   </si>
   <si>
-    <t xml:space="preserve">шт.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Новых компаний за месяц</t>
-  </si>
-  <si>
     <t xml:space="preserve">Средний платёж</t>
   </si>
   <si>
@@ -168,21 +168,21 @@
     <t xml:space="preserve">Выручка Труда</t>
   </si>
   <si>
+    <t xml:space="preserve">Визитов на платное предложение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">чел./мес</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Новых подписчиков за месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">чел.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Платных подписчиков</t>
   </si>
   <si>
-    <t xml:space="preserve">чел.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Новых подписчиков за месяц</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Визитов на платное предложение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">чел./мес</t>
-  </si>
-  <si>
     <t xml:space="preserve">Выручка подписки</t>
   </si>
   <si>
@@ -207,7 +207,7 @@
     <t xml:space="preserve">Выручка всего</t>
   </si>
   <si>
-    <t xml:space="preserve">ARR (без сделок с брендами)</t>
+    <t xml:space="preserve">ARR (без брендов и пилотов)</t>
   </si>
   <si>
     <t xml:space="preserve">$</t>
@@ -237,10 +237,25 @@
     <t xml:space="preserve">Деньги на счету</t>
   </si>
   <si>
+    <t xml:space="preserve">Сверка с бюджетом этапов (должно быть 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этап 1: расход по месяцам минус бюджет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этап 2: расход по месяцам минус бюджет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этап 3: расход по месяцам минус бюджет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этап 4: расход по месяцам минус бюджет</t>
+  </si>
+  <si>
     <t xml:space="preserve">Сходимость со стратегией</t>
   </si>
   <si>
-    <t xml:space="preserve">Модель считает по своим формулам, колонка «В стратегии» — то, что написано в target-state-18m.md и деке v10. Расхождение означает, что в одном из двух мест цифру надо поправить.</t>
+    <t xml:space="preserve">Модель считает по своим формулам, колонка «В стратегии» — то, что написано в target-state-18m.md и деке v10. «Не меньше» — цель со знаком «+», засчитывается от 85%. Расхождение означает, что в одном из двух мест цифру надо поправить.</t>
   </si>
   <si>
     <t xml:space="preserve">Что сверяем</t>
@@ -258,7 +273,10 @@
     <t xml:space="preserve">ARR группы в 18-м месяце</t>
   </si>
   <si>
-    <t xml:space="preserve">Выручка 18-го месяца</t>
+    <t xml:space="preserve">Выручка 18-го месяца без брендов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка 18-го месяца с брендами</t>
   </si>
   <si>
     <t xml:space="preserve">Расход 18-го месяца</t>
@@ -270,33 +288,44 @@
     <t xml:space="preserve">Деньги на счету в 18-м месяце</t>
   </si>
   <si>
-    <t xml:space="preserve">Платящих компаний, Труд</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подписчиков, Личность</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Платящих компаний, Капитал</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Визитов на оплату в месяц, Личность</t>
+    <t xml:space="preserve">Труд: база в мес. 6, не меньше</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Труд: база в мес. 15, не меньше</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Труд: база в мес. 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Капитал: база в мес. 6, не меньше</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Капитал: база в мес. 15, не меньше</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Капитал: база в мес. 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Личность: подписчиков в мес. 18</t>
   </si>
   <si>
     <t xml:space="preserve">Штат к 18-му месяцу</t>
   </si>
   <si>
-    <t xml:space="preserve">Допуск подобран под порядок величины показателя; он в формуле колонки «Сходится».</t>
+    <t xml:space="preserve">Допуск для точных целей — в формуле колонки «Сходится», под порядок величины.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -441,7 +470,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -490,11 +519,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -502,8 +531,16 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1067,7 +1104,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:T38"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -1188,49 +1225,49 @@
         <v>0</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>0</v>
+        <v>1.4558</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0</v>
+        <v>2.9116</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>10</v>
+        <v>4.3674</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>13.4801</v>
+        <v>5.6395</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>18.1712</v>
+        <v>6.9116</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>24.4949</v>
+        <v>8.1837</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>33.0193</v>
+        <v>9.4558</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>44.5102</v>
+        <v>10.7279</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>70.433</v>
+        <v>13.5</v>
       </c>
       <c r="P6" s="12" t="n">
-        <v>82.68</v>
+        <v>15</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>97.0567</v>
+        <v>16.5</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>113.9332</v>
+        <v>18</v>
       </c>
       <c r="S6" s="12" t="n">
-        <v>133.7442</v>
+        <v>19.5</v>
       </c>
       <c r="T6" s="12" t="n">
-        <v>157</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1245,72 +1282,72 @@
         <v>0</v>
       </c>
       <c r="D7" s="13" t="n">
-        <f aca="false">D6-C6*(1-Рычаги!$B$8)</f>
+        <f aca="false">C7*(1-Рычаги!$B$8)+D6</f>
         <v>0</v>
       </c>
       <c r="E7" s="13" t="n">
-        <f aca="false">E6-D6*(1-Рычаги!$B$8)</f>
+        <f aca="false">D7*(1-Рычаги!$B$8)+E6</f>
         <v>0</v>
       </c>
       <c r="F7" s="13" t="n">
-        <f aca="false">F6-E6*(1-Рычаги!$B$8)</f>
-        <v>0</v>
+        <f aca="false">E7*(1-Рычаги!$B$8)+F6</f>
+        <v>1.4558</v>
       </c>
       <c r="G7" s="13" t="n">
-        <f aca="false">G6-F6*(1-Рычаги!$B$8)</f>
-        <v>0</v>
+        <f aca="false">F7*(1-Рычаги!$B$8)+G6</f>
+        <v>4.352842</v>
       </c>
       <c r="H7" s="13" t="n">
-        <f aca="false">H6-G6*(1-Рычаги!$B$8)</f>
-        <v>10</v>
+        <f aca="false">G7*(1-Рычаги!$B$8)+H6</f>
+        <v>8.67671358</v>
       </c>
       <c r="I7" s="13" t="n">
-        <f aca="false">I6-H6*(1-Рычаги!$B$8)</f>
-        <v>3.5801</v>
+        <f aca="false">H7*(1-Рычаги!$B$8)+I6</f>
+        <v>14.2294464442</v>
       </c>
       <c r="J7" s="13" t="n">
-        <f aca="false">J6-I6*(1-Рычаги!$B$8)</f>
-        <v>4.825901</v>
+        <f aca="false">I7*(1-Рычаги!$B$8)+J6</f>
+        <v>20.998751979758</v>
       </c>
       <c r="K7" s="13" t="n">
-        <f aca="false">K6-J6*(1-Рычаги!$B$8)</f>
-        <v>6.505412</v>
+        <f aca="false">J7*(1-Рычаги!$B$8)+K6</f>
+        <v>28.9724644599604</v>
       </c>
       <c r="L7" s="13" t="n">
-        <f aca="false">L6-K6*(1-Рычаги!$B$8)</f>
-        <v>8.769349</v>
+        <f aca="false">K7*(1-Рычаги!$B$8)+L6</f>
+        <v>38.1385398153608</v>
       </c>
       <c r="M7" s="13" t="n">
-        <f aca="false">M6-L6*(1-Рычаги!$B$8)</f>
-        <v>11.821093</v>
+        <f aca="false">L7*(1-Рычаги!$B$8)+M6</f>
+        <v>48.4850544172072</v>
       </c>
       <c r="N7" s="13" t="n">
-        <f aca="false">N6-M6*(1-Рычаги!$B$8)</f>
-        <v>15.934902</v>
+        <f aca="false">M7*(1-Рычаги!$B$8)+N6</f>
+        <v>60.0002038730351</v>
       </c>
       <c r="O7" s="13" t="n">
-        <f aca="false">O6-N6*(1-Рычаги!$B$8)</f>
-        <v>11.033</v>
+        <f aca="false">N7*(1-Рычаги!$B$8)+O6</f>
+        <v>72.9002018343048</v>
       </c>
       <c r="P7" s="13" t="n">
-        <f aca="false">P6-O6*(1-Рычаги!$B$8)</f>
-        <v>12.95133</v>
+        <f aca="false">O7*(1-Рычаги!$B$8)+P6</f>
+        <v>87.1711998159617</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <f aca="false">Q6-P6*(1-Рычаги!$B$8)</f>
-        <v>15.2035</v>
+        <f aca="false">P7*(1-Рычаги!$B$8)+Q6</f>
+        <v>102.799487817802</v>
       </c>
       <c r="R7" s="13" t="n">
-        <f aca="false">R6-Q6*(1-Рычаги!$B$8)</f>
-        <v>17.847067</v>
+        <f aca="false">Q7*(1-Рычаги!$B$8)+R6</f>
+        <v>119.771492939624</v>
       </c>
       <c r="S7" s="13" t="n">
-        <f aca="false">S6-R6*(1-Рычаги!$B$8)</f>
-        <v>20.950332</v>
+        <f aca="false">R7*(1-Рычаги!$B$8)+S6</f>
+        <v>138.073778010228</v>
       </c>
       <c r="T7" s="13" t="n">
-        <f aca="false">T6-S6*(1-Рычаги!$B$8)</f>
-        <v>24.593242</v>
+        <f aca="false">S7*(1-Рычаги!$B$8)+T6</f>
+        <v>157.693040230126</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1400,139 +1437,139 @@
       <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="n">
+      <c r="C9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="12" t="n">
+      <c r="H9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="14" t="n">
-        <f aca="false">C6*C8+C9*Рычаги!$B$9</f>
+        <f aca="false">C7*C8+C9*Рычаги!$B$9</f>
         <v>0</v>
       </c>
       <c r="D10" s="14" t="n">
-        <f aca="false">D6*D8+D9*Рычаги!$B$9</f>
+        <f aca="false">D7*D8+D9*Рычаги!$B$9</f>
         <v>4000</v>
       </c>
       <c r="E10" s="14" t="n">
-        <f aca="false">E6*E8+E9*Рычаги!$B$9</f>
+        <f aca="false">E7*E8+E9*Рычаги!$B$9</f>
         <v>8000</v>
       </c>
       <c r="F10" s="14" t="n">
-        <f aca="false">F6*F8+F9*Рычаги!$B$9</f>
+        <f aca="false">F7*F8+F9*Рычаги!$B$9</f>
         <v>8000</v>
       </c>
       <c r="G10" s="14" t="n">
-        <f aca="false">G6*G8+G9*Рычаги!$B$9</f>
+        <f aca="false">G7*G8+G9*Рычаги!$B$9</f>
         <v>8000</v>
       </c>
       <c r="H10" s="14" t="n">
-        <f aca="false">H6*H8+H9*Рычаги!$B$9</f>
-        <v>50000</v>
+        <f aca="false">H7*H8+H9*Рычаги!$B$9</f>
+        <v>43383.5679</v>
       </c>
       <c r="I10" s="14" t="n">
-        <f aca="false">I6*I8+I9*Рычаги!$B$9</f>
-        <v>78633.9166666667</v>
+        <f aca="false">I7*I8+I9*Рычаги!$B$9</f>
+        <v>83005.1042578333</v>
       </c>
       <c r="J10" s="14" t="n">
-        <f aca="false">J6*J8+J9*Рычаги!$B$9</f>
-        <v>121141.333333333</v>
+        <f aca="false">J7*J8+J9*Рычаги!$B$9</f>
+        <v>139991.679865053</v>
       </c>
       <c r="K10" s="14" t="n">
-        <f aca="false">K6*K8+K9*Рычаги!$B$9</f>
-        <v>183711.75</v>
+        <f aca="false">K7*K8+K9*Рычаги!$B$9</f>
+        <v>217293.483449703</v>
       </c>
       <c r="L10" s="14" t="n">
-        <f aca="false">L6*L8+L9*Рычаги!$B$9</f>
-        <v>275160.833333333</v>
+        <f aca="false">L7*L8+L9*Рычаги!$B$9</f>
+        <v>317821.165128007</v>
       </c>
       <c r="M10" s="14" t="n">
-        <f aca="false">M6*M8+M9*Рычаги!$B$9</f>
-        <v>408010.166666667</v>
+        <f aca="false">M7*M8+M9*Рычаги!$B$9</f>
+        <v>444446.332157733</v>
       </c>
       <c r="N10" s="14" t="n">
-        <f aca="false">N6*N8+N9*Рычаги!$B$9</f>
-        <v>600000</v>
+        <f aca="false">N7*N8+N9*Рычаги!$B$9</f>
+        <v>600002.038730351</v>
       </c>
       <c r="O10" s="14" t="n">
-        <f aca="false">O6*O8+O9*Рычаги!$B$9</f>
-        <v>763024.166666667</v>
+        <f aca="false">O7*O8+O9*Рычаги!$B$9</f>
+        <v>789752.186538302</v>
       </c>
       <c r="P10" s="14" t="n">
-        <f aca="false">P6*P8+P9*Рычаги!$B$9</f>
-        <v>964600</v>
+        <f aca="false">P7*P8+P9*Рычаги!$B$9</f>
+        <v>1016997.33118622</v>
       </c>
       <c r="Q10" s="14" t="n">
-        <f aca="false">Q6*Q8+Q9*Рычаги!$B$9</f>
-        <v>1213208.75</v>
+        <f aca="false">Q7*Q8+Q9*Рычаги!$B$9</f>
+        <v>1284993.59772253</v>
       </c>
       <c r="R10" s="14" t="n">
-        <f aca="false">R6*R8+R9*Рычаги!$B$9</f>
-        <v>1519109.33333333</v>
+        <f aca="false">R7*R8+R9*Рычаги!$B$9</f>
+        <v>1596953.23919499</v>
       </c>
       <c r="S10" s="14" t="n">
-        <f aca="false">S6*S8+S9*Рычаги!$B$9</f>
-        <v>1894709.5</v>
+        <f aca="false">S7*S8+S9*Рычаги!$B$9</f>
+        <v>1956045.18847823</v>
       </c>
       <c r="T10" s="14" t="n">
-        <f aca="false">T6*T8+T9*Рычаги!$B$9</f>
-        <v>2355000</v>
+        <f aca="false">T7*T8+T9*Рычаги!$B$9</f>
+        <v>2365395.60345188</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1566,59 +1603,59 @@
       <c r="B12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>2500</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>7500</v>
-      </c>
-      <c r="N12" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="O12" s="12" t="n">
-        <v>13572.0881</v>
-      </c>
-      <c r="P12" s="12" t="n">
-        <v>18420.1575</v>
-      </c>
-      <c r="Q12" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="R12" s="12" t="n">
-        <v>34110.2247</v>
-      </c>
-      <c r="S12" s="12" t="n">
-        <v>46540.2973</v>
-      </c>
-      <c r="T12" s="12" t="n">
-        <v>63500</v>
+      <c r="C12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>108324.8984</v>
+      </c>
+      <c r="L12" s="15" t="n">
+        <v>216649.7969</v>
+      </c>
+      <c r="M12" s="15" t="n">
+        <v>324974.6953</v>
+      </c>
+      <c r="N12" s="15" t="n">
+        <v>433299.5937</v>
+      </c>
+      <c r="O12" s="15" t="n">
+        <v>525208.7109</v>
+      </c>
+      <c r="P12" s="15" t="n">
+        <v>617117.8281</v>
+      </c>
+      <c r="Q12" s="15" t="n">
+        <v>709026.9453</v>
+      </c>
+      <c r="R12" s="15" t="n">
+        <v>1006017.9635</v>
+      </c>
+      <c r="S12" s="15" t="n">
+        <v>1303008.9818</v>
+      </c>
+      <c r="T12" s="15" t="n">
+        <v>1600000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1626,159 +1663,159 @@
         <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <f aca="false">C12</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <f aca="false">MAX(0,D12-C12*(1-Рычаги!$B$13))</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <f aca="false">MAX(0,E12-D12*(1-Рычаги!$B$13))</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <f aca="false">MAX(0,F12-E12*(1-Рычаги!$B$13))</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <f aca="false">MAX(0,G12-F12*(1-Рычаги!$B$13))</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <f aca="false">MAX(0,H12-G12*(1-Рычаги!$B$13))</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <f aca="false">MAX(0,I12-H12*(1-Рычаги!$B$13))</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <f aca="false">MAX(0,J12-I12*(1-Рычаги!$B$13))</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <f aca="false">MAX(0,K12-J12*(1-Рычаги!$B$13))</f>
-        <v>2500</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <f aca="false">MAX(0,L12-K12*(1-Рычаги!$B$13))</f>
-        <v>2700</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <f aca="false">MAX(0,M12-L12*(1-Рычаги!$B$13))</f>
-        <v>2900</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <f aca="false">MAX(0,N12-M12*(1-Рычаги!$B$13))</f>
-        <v>3100</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <f aca="false">MAX(0,O12-N12*(1-Рычаги!$B$13))</f>
-        <v>4372.0881</v>
-      </c>
-      <c r="P13" s="13" t="n">
-        <f aca="false">MAX(0,P12-O12*(1-Рычаги!$B$13))</f>
-        <v>5933.836448</v>
-      </c>
-      <c r="Q13" s="13" t="n">
-        <f aca="false">MAX(0,Q12-P12*(1-Рычаги!$B$13))</f>
-        <v>8053.4551</v>
-      </c>
-      <c r="R13" s="13" t="n">
-        <f aca="false">MAX(0,R12-Q12*(1-Рычаги!$B$13))</f>
-        <v>11110.2247</v>
-      </c>
-      <c r="S13" s="13" t="n">
-        <f aca="false">MAX(0,S12-R12*(1-Рычаги!$B$13))</f>
-        <v>15158.890576</v>
-      </c>
-      <c r="T13" s="13" t="n">
-        <f aca="false">MAX(0,T12-S12*(1-Рычаги!$B$13))</f>
-        <v>20682.926484</v>
+        <v>51</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <f aca="false">C12*Рычаги!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <f aca="false">D12*Рычаги!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <f aca="false">E12*Рычаги!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <f aca="false">F12*Рычаги!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <f aca="false">G12*Рычаги!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <f aca="false">H12*Рычаги!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <f aca="false">I12*Рычаги!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <f aca="false">J12*Рычаги!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <f aca="false">K12*Рычаги!$B$14</f>
+        <v>1083.248984</v>
+      </c>
+      <c r="L13" s="17" t="n">
+        <f aca="false">L12*Рычаги!$B$14</f>
+        <v>2166.497969</v>
+      </c>
+      <c r="M13" s="17" t="n">
+        <f aca="false">M12*Рычаги!$B$14</f>
+        <v>3249.746953</v>
+      </c>
+      <c r="N13" s="17" t="n">
+        <f aca="false">N12*Рычаги!$B$14</f>
+        <v>4332.995937</v>
+      </c>
+      <c r="O13" s="17" t="n">
+        <f aca="false">O12*Рычаги!$B$14</f>
+        <v>5252.087109</v>
+      </c>
+      <c r="P13" s="17" t="n">
+        <f aca="false">P12*Рычаги!$B$14</f>
+        <v>6171.178281</v>
+      </c>
+      <c r="Q13" s="17" t="n">
+        <f aca="false">Q12*Рычаги!$B$14</f>
+        <v>7090.269453</v>
+      </c>
+      <c r="R13" s="17" t="n">
+        <f aca="false">R12*Рычаги!$B$14</f>
+        <v>10060.179635</v>
+      </c>
+      <c r="S13" s="17" t="n">
+        <f aca="false">S12*Рычаги!$B$14</f>
+        <v>13030.089818</v>
+      </c>
+      <c r="T13" s="17" t="n">
+        <f aca="false">T12*Рычаги!$B$14</f>
+        <v>16000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <f aca="false">C13/Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <f aca="false">D13/Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <f aca="false">E13/Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <f aca="false">F13/Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <f aca="false">G13/Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <f aca="false">H13/Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <f aca="false">I13/Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <f aca="false">J13/Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="13" t="n">
-        <f aca="false">K13/Рычаги!$B$14</f>
-        <v>250000</v>
-      </c>
-      <c r="L14" s="13" t="n">
-        <f aca="false">L13/Рычаги!$B$14</f>
-        <v>270000</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <f aca="false">M13/Рычаги!$B$14</f>
-        <v>290000</v>
-      </c>
-      <c r="N14" s="13" t="n">
-        <f aca="false">N13/Рычаги!$B$14</f>
-        <v>310000</v>
-      </c>
-      <c r="O14" s="13" t="n">
-        <f aca="false">O13/Рычаги!$B$14</f>
-        <v>437208.81</v>
-      </c>
-      <c r="P14" s="13" t="n">
-        <f aca="false">P13/Рычаги!$B$14</f>
-        <v>593383.6448</v>
-      </c>
-      <c r="Q14" s="13" t="n">
-        <f aca="false">Q13/Рычаги!$B$14</f>
-        <v>805345.51</v>
-      </c>
-      <c r="R14" s="13" t="n">
-        <f aca="false">R13/Рычаги!$B$14</f>
-        <v>1111022.47</v>
-      </c>
-      <c r="S14" s="13" t="n">
-        <f aca="false">S13/Рычаги!$B$14</f>
-        <v>1515889.0576</v>
-      </c>
-      <c r="T14" s="13" t="n">
-        <f aca="false">T13/Рычаги!$B$14</f>
-        <v>2068292.6484</v>
+      <c r="C14" s="17" t="n">
+        <f aca="false">C13</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <f aca="false">C14*(1-Рычаги!$B$13)+D13</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <f aca="false">D14*(1-Рычаги!$B$13)+E13</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <f aca="false">E14*(1-Рычаги!$B$13)+F13</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <f aca="false">F14*(1-Рычаги!$B$13)+G13</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <f aca="false">G14*(1-Рычаги!$B$13)+H13</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <f aca="false">H14*(1-Рычаги!$B$13)+I13</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <f aca="false">I14*(1-Рычаги!$B$13)+J13</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <f aca="false">J14*(1-Рычаги!$B$13)+K13</f>
+        <v>1083.248984</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <f aca="false">K14*(1-Рычаги!$B$13)+L13</f>
+        <v>3163.08703428</v>
+      </c>
+      <c r="M14" s="17" t="n">
+        <f aca="false">L14*(1-Рычаги!$B$13)+M13</f>
+        <v>6159.7870245376</v>
+      </c>
+      <c r="N14" s="17" t="n">
+        <f aca="false">M14*(1-Рычаги!$B$13)+N13</f>
+        <v>9999.99999957459</v>
+      </c>
+      <c r="O14" s="17" t="n">
+        <f aca="false">N14*(1-Рычаги!$B$13)+O13</f>
+        <v>14452.0871086086</v>
+      </c>
+      <c r="P14" s="17" t="n">
+        <f aca="false">O14*(1-Рычаги!$B$13)+P13</f>
+        <v>19467.0984209199</v>
+      </c>
+      <c r="Q14" s="17" t="n">
+        <f aca="false">P14*(1-Рычаги!$B$13)+Q13</f>
+        <v>25000.0000002463</v>
+      </c>
+      <c r="R14" s="17" t="n">
+        <f aca="false">Q14*(1-Рычаги!$B$13)+R13</f>
+        <v>33060.1796352266</v>
+      </c>
+      <c r="S14" s="17" t="n">
+        <f aca="false">R14*(1-Рычаги!$B$13)+S13</f>
+        <v>43445.4550824085</v>
+      </c>
+      <c r="T14" s="17" t="n">
+        <f aca="false">S14*(1-Рычаги!$B$13)+T13</f>
+        <v>55969.8186758158</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1789,76 +1826,76 @@
         <v>45</v>
       </c>
       <c r="C15" s="14" t="n">
-        <f aca="false">C12*Рычаги!$B$12</f>
+        <f aca="false">C14*Рычаги!$B$12</f>
         <v>0</v>
       </c>
       <c r="D15" s="14" t="n">
-        <f aca="false">D12*Рычаги!$B$12</f>
+        <f aca="false">D14*Рычаги!$B$12</f>
         <v>0</v>
       </c>
       <c r="E15" s="14" t="n">
-        <f aca="false">E12*Рычаги!$B$12</f>
+        <f aca="false">E14*Рычаги!$B$12</f>
         <v>0</v>
       </c>
       <c r="F15" s="14" t="n">
-        <f aca="false">F12*Рычаги!$B$12</f>
+        <f aca="false">F14*Рычаги!$B$12</f>
         <v>0</v>
       </c>
       <c r="G15" s="14" t="n">
-        <f aca="false">G12*Рычаги!$B$12</f>
+        <f aca="false">G14*Рычаги!$B$12</f>
         <v>0</v>
       </c>
       <c r="H15" s="14" t="n">
-        <f aca="false">H12*Рычаги!$B$12</f>
+        <f aca="false">H14*Рычаги!$B$12</f>
         <v>0</v>
       </c>
       <c r="I15" s="14" t="n">
-        <f aca="false">I12*Рычаги!$B$12</f>
+        <f aca="false">I14*Рычаги!$B$12</f>
         <v>0</v>
       </c>
       <c r="J15" s="14" t="n">
-        <f aca="false">J12*Рычаги!$B$12</f>
+        <f aca="false">J14*Рычаги!$B$12</f>
         <v>0</v>
       </c>
       <c r="K15" s="14" t="n">
-        <f aca="false">K12*Рычаги!$B$12</f>
-        <v>25000</v>
+        <f aca="false">K14*Рычаги!$B$12</f>
+        <v>10832.48984</v>
       </c>
       <c r="L15" s="14" t="n">
-        <f aca="false">L12*Рычаги!$B$12</f>
-        <v>50000</v>
+        <f aca="false">L14*Рычаги!$B$12</f>
+        <v>31630.8703428</v>
       </c>
       <c r="M15" s="14" t="n">
-        <f aca="false">M12*Рычаги!$B$12</f>
-        <v>75000</v>
+        <f aca="false">M14*Рычаги!$B$12</f>
+        <v>61597.870245376</v>
       </c>
       <c r="N15" s="14" t="n">
-        <f aca="false">N12*Рычаги!$B$12</f>
-        <v>100000</v>
+        <f aca="false">N14*Рычаги!$B$12</f>
+        <v>99999.9999957459</v>
       </c>
       <c r="O15" s="14" t="n">
-        <f aca="false">O12*Рычаги!$B$12</f>
-        <v>135720.881</v>
+        <f aca="false">O14*Рычаги!$B$12</f>
+        <v>144520.871086086</v>
       </c>
       <c r="P15" s="14" t="n">
-        <f aca="false">P12*Рычаги!$B$12</f>
-        <v>184201.575</v>
+        <f aca="false">P14*Рычаги!$B$12</f>
+        <v>194670.984209199</v>
       </c>
       <c r="Q15" s="14" t="n">
-        <f aca="false">Q12*Рычаги!$B$12</f>
-        <v>250000</v>
+        <f aca="false">Q14*Рычаги!$B$12</f>
+        <v>250000.000002463</v>
       </c>
       <c r="R15" s="14" t="n">
-        <f aca="false">R12*Рычаги!$B$12</f>
-        <v>341102.247</v>
+        <f aca="false">R14*Рычаги!$B$12</f>
+        <v>330601.796352266</v>
       </c>
       <c r="S15" s="14" t="n">
-        <f aca="false">S12*Рычаги!$B$12</f>
-        <v>465402.973</v>
+        <f aca="false">S14*Рычаги!$B$12</f>
+        <v>434454.550824085</v>
       </c>
       <c r="T15" s="14" t="n">
-        <f aca="false">T12*Рычаги!$B$12</f>
-        <v>635000</v>
+        <f aca="false">T14*Рычаги!$B$12</f>
+        <v>559698.186758158</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1887,37 +1924,37 @@
         <v>1</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>1.2599</v>
+        <v>2</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>1.5874</v>
+        <v>3</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2.5198</v>
+        <v>4</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>3.1748</v>
+        <v>4</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>4.4898</v>
+        <v>4.6667</v>
       </c>
       <c r="P16" s="12" t="n">
-        <v>5.0397</v>
+        <v>5.3333</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>5.6569</v>
+        <v>6</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>6.3496</v>
+        <v>6.6667</v>
       </c>
       <c r="S16" s="12" t="n">
-        <v>7.1272</v>
+        <v>7.3333</v>
       </c>
       <c r="T16" s="12" t="n">
         <v>8</v>
@@ -1956,23 +1993,23 @@
       </c>
       <c r="I17" s="14" t="n">
         <f aca="false">I16*Рычаги!$B$15</f>
-        <v>62995</v>
+        <v>100000</v>
       </c>
       <c r="J17" s="14" t="n">
         <f aca="false">J16*Рычаги!$B$15</f>
-        <v>79370</v>
+        <v>150000</v>
       </c>
       <c r="K17" s="14" t="n">
         <f aca="false">K16*Рычаги!$B$15</f>
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="L17" s="14" t="n">
         <f aca="false">L16*Рычаги!$B$15</f>
-        <v>125990</v>
+        <v>200000</v>
       </c>
       <c r="M17" s="14" t="n">
         <f aca="false">M16*Рычаги!$B$15</f>
-        <v>158740</v>
+        <v>200000</v>
       </c>
       <c r="N17" s="14" t="n">
         <f aca="false">N16*Рычаги!$B$15</f>
@@ -1980,23 +2017,23 @@
       </c>
       <c r="O17" s="14" t="n">
         <f aca="false">O16*Рычаги!$B$15</f>
-        <v>224490</v>
+        <v>233335</v>
       </c>
       <c r="P17" s="14" t="n">
         <f aca="false">P16*Рычаги!$B$15</f>
-        <v>251985</v>
+        <v>266665</v>
       </c>
       <c r="Q17" s="14" t="n">
         <f aca="false">Q16*Рычаги!$B$15</f>
-        <v>282845</v>
+        <v>300000</v>
       </c>
       <c r="R17" s="14" t="n">
         <f aca="false">R16*Рычаги!$B$15</f>
-        <v>317480</v>
+        <v>333335</v>
       </c>
       <c r="S17" s="14" t="n">
         <f aca="false">S16*Рычаги!$B$15</f>
-        <v>356360</v>
+        <v>366665</v>
       </c>
       <c r="T17" s="14" t="n">
         <f aca="false">T16*Рычаги!$B$15</f>
@@ -2029,7 +2066,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>42</v>
@@ -2044,54 +2081,54 @@
         <v>2</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>3.42</v>
+        <v>3.5851</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>5.848</v>
+        <v>5.1702</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>10</v>
+        <v>6.7553</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>14.678</v>
+        <v>8.9628</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>21.5443</v>
+        <v>11.1702</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>31.6228</v>
+        <v>13.3777</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>46.4159</v>
+        <v>15.5851</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>68.1292</v>
+        <v>17.7926</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>116.9607</v>
+        <v>24.1667</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>136.7981</v>
+        <v>28.3333</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>160</v>
+        <v>32.5</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>187.1371</v>
+        <v>36.6667</v>
       </c>
       <c r="S19" s="12" t="n">
-        <v>218.8769</v>
+        <v>40.8333</v>
       </c>
       <c r="T19" s="12" t="n">
-        <v>256</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>42</v>
@@ -2101,72 +2138,72 @@
         <v>0</v>
       </c>
       <c r="D20" s="13" t="n">
-        <f aca="false">MAX(0,D19-C19*(1-Рычаги!$B$19))</f>
+        <f aca="false">C20*(1-Рычаги!$B$19)+D19</f>
         <v>0</v>
       </c>
       <c r="E20" s="13" t="n">
-        <f aca="false">MAX(0,E19-D19*(1-Рычаги!$B$19))</f>
+        <f aca="false">D20*(1-Рычаги!$B$19)+E19</f>
         <v>2</v>
       </c>
       <c r="F20" s="13" t="n">
-        <f aca="false">MAX(0,F19-E19*(1-Рычаги!$B$19))</f>
-        <v>1.45</v>
+        <f aca="false">E20*(1-Рычаги!$B$19)+F19</f>
+        <v>5.5551</v>
       </c>
       <c r="G20" s="13" t="n">
-        <f aca="false">MAX(0,G19-F19*(1-Рычаги!$B$19))</f>
-        <v>2.4793</v>
+        <f aca="false">F20*(1-Рычаги!$B$19)+G19</f>
+        <v>10.6419735</v>
       </c>
       <c r="H20" s="13" t="n">
-        <f aca="false">MAX(0,H19-G19*(1-Рычаги!$B$19))</f>
-        <v>4.23972</v>
+        <f aca="false">G20*(1-Рычаги!$B$19)+H19</f>
+        <v>17.2376438975</v>
       </c>
       <c r="I20" s="13" t="n">
-        <f aca="false">MAX(0,I19-H19*(1-Рычаги!$B$19))</f>
-        <v>4.828</v>
+        <f aca="false">H20*(1-Рычаги!$B$19)+I19</f>
+        <v>25.9418792390375</v>
       </c>
       <c r="J20" s="13" t="n">
-        <f aca="false">MAX(0,J19-I19*(1-Рычаги!$B$19))</f>
-        <v>7.08647</v>
+        <f aca="false">I20*(1-Рычаги!$B$19)+J19</f>
+        <v>36.7229510504519</v>
       </c>
       <c r="K20" s="13" t="n">
-        <f aca="false">MAX(0,K19-J19*(1-Рычаги!$B$19))</f>
-        <v>10.4016645</v>
+        <f aca="false">J20*(1-Рычаги!$B$19)+K19</f>
+        <v>49.5498067846952</v>
       </c>
       <c r="L20" s="13" t="n">
-        <f aca="false">MAX(0,L19-K19*(1-Рычаги!$B$19))</f>
-        <v>15.267442</v>
+        <f aca="false">K20*(1-Рычаги!$B$19)+L19</f>
+        <v>64.3916596829247</v>
       </c>
       <c r="M20" s="13" t="n">
-        <f aca="false">MAX(0,M19-L19*(1-Рычаги!$B$19))</f>
-        <v>22.4095385</v>
+        <f aca="false">L20*(1-Рычаги!$B$19)+M19</f>
+        <v>81.2183847876809</v>
       </c>
       <c r="N20" s="13" t="n">
-        <f aca="false">MAX(0,N19-M19*(1-Рычаги!$B$19))</f>
-        <v>32.892738</v>
+        <f aca="false">M20*(1-Рычаги!$B$19)+N19</f>
+        <v>100.000109015866</v>
       </c>
       <c r="O20" s="13" t="n">
-        <f aca="false">MAX(0,O19-N19*(1-Рычаги!$B$19))</f>
-        <v>18.4607</v>
+        <f aca="false">N20*(1-Рычаги!$B$19)+O19</f>
+        <v>122.666807380628</v>
       </c>
       <c r="P20" s="13" t="n">
-        <f aca="false">MAX(0,P19-O19*(1-Рычаги!$B$19))</f>
-        <v>21.5918105</v>
+        <f aca="false">O20*(1-Рычаги!$B$19)+P19</f>
+        <v>149.160105269918</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <f aca="false">MAX(0,Q19-P19*(1-Рычаги!$B$19))</f>
-        <v>25.2538715</v>
+        <f aca="false">P20*(1-Рычаги!$B$19)+Q19</f>
+        <v>179.422703690869</v>
       </c>
       <c r="R20" s="13" t="n">
-        <f aca="false">MAX(0,R19-Q19*(1-Рычаги!$B$19))</f>
-        <v>29.5371</v>
+        <f aca="false">Q20*(1-Рычаги!$B$19)+R19</f>
+        <v>213.398063135506</v>
       </c>
       <c r="S20" s="13" t="n">
-        <f aca="false">MAX(0,S19-R19*(1-Рычаги!$B$19))</f>
-        <v>34.5468565</v>
+        <f aca="false">R20*(1-Рычаги!$B$19)+S19</f>
+        <v>251.030392188474</v>
       </c>
       <c r="T20" s="13" t="n">
-        <f aca="false">MAX(0,T19-S19*(1-Рычаги!$B$19))</f>
-        <v>40.4062535</v>
+        <f aca="false">S20*(1-Рычаги!$B$19)+T19</f>
+        <v>292.264936305647</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2250,83 +2287,83 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="14" t="n">
-        <f aca="false">C19*C21</f>
+        <f aca="false">C20*C21</f>
         <v>0</v>
       </c>
       <c r="D22" s="14" t="n">
-        <f aca="false">D19*D21</f>
+        <f aca="false">D20*D21</f>
         <v>0</v>
       </c>
       <c r="E22" s="14" t="n">
-        <f aca="false">E19*E21</f>
+        <f aca="false">E20*E21</f>
         <v>1600</v>
       </c>
       <c r="F22" s="14" t="n">
-        <f aca="false">F19*F21</f>
-        <v>3009.6</v>
+        <f aca="false">F20*F21</f>
+        <v>4888.488</v>
       </c>
       <c r="G22" s="14" t="n">
-        <f aca="false">G19*G21</f>
-        <v>5614.08</v>
+        <f aca="false">G20*G21</f>
+        <v>10216.29456</v>
       </c>
       <c r="H22" s="14" t="n">
-        <f aca="false">H19*H21</f>
-        <v>10400</v>
+        <f aca="false">H20*H21</f>
+        <v>17927.1496534</v>
       </c>
       <c r="I22" s="14" t="n">
-        <f aca="false">I19*I21</f>
-        <v>16439.36</v>
+        <f aca="false">I20*I21</f>
+        <v>29054.904747722</v>
       </c>
       <c r="J22" s="14" t="n">
-        <f aca="false">J19*J21</f>
-        <v>25853.16</v>
+        <f aca="false">J20*J21</f>
+        <v>44067.5412605423</v>
       </c>
       <c r="K22" s="14" t="n">
-        <f aca="false">K19*K21</f>
-        <v>40477.184</v>
+        <f aca="false">K20*K21</f>
+        <v>63423.7526844098</v>
       </c>
       <c r="L22" s="14" t="n">
-        <f aca="false">L19*L21</f>
-        <v>63125.624</v>
+        <f aca="false">L20*L21</f>
+        <v>87572.6571687776</v>
       </c>
       <c r="M22" s="14" t="n">
-        <f aca="false">M19*M21</f>
-        <v>98106.048</v>
+        <f aca="false">M20*M21</f>
+        <v>116954.47409426</v>
       </c>
       <c r="N22" s="14" t="n">
-        <f aca="false">N19*N21</f>
-        <v>152000</v>
+        <f aca="false">N20*N21</f>
+        <v>152000.165704116</v>
       </c>
       <c r="O22" s="14" t="n">
-        <f aca="false">O19*O21</f>
-        <v>187137.12</v>
+        <f aca="false">O20*O21</f>
+        <v>196266.891809004</v>
       </c>
       <c r="P22" s="14" t="n">
-        <f aca="false">P19*P21</f>
-        <v>229820.808</v>
+        <f aca="false">P20*P21</f>
+        <v>250588.976853463</v>
       </c>
       <c r="Q22" s="14" t="n">
-        <f aca="false">Q19*Q21</f>
-        <v>281600</v>
+        <f aca="false">Q20*Q21</f>
+        <v>315783.95849593</v>
       </c>
       <c r="R22" s="14" t="n">
-        <f aca="false">R19*R21</f>
-        <v>344332.264</v>
+        <f aca="false">R20*R21</f>
+        <v>392652.436169332</v>
       </c>
       <c r="S22" s="14" t="n">
-        <f aca="false">S19*S21</f>
-        <v>420243.648</v>
+        <f aca="false">S20*S21</f>
+        <v>481978.35300187</v>
       </c>
       <c r="T22" s="14" t="n">
-        <f aca="false">T19*T21</f>
-        <v>512000</v>
+        <f aca="false">T20*T21</f>
+        <v>584529.872611294</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2354,7 +2391,7 @@
       <c r="T23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -2374,63 +2411,63 @@
       </c>
       <c r="F24" s="14" t="n">
         <f aca="false">F10+F15+F17+F22</f>
-        <v>61009.6</v>
+        <v>62888.488</v>
       </c>
       <c r="G24" s="14" t="n">
         <f aca="false">G10+G15+G17+G22</f>
-        <v>63614.08</v>
+        <v>68216.29456</v>
       </c>
       <c r="H24" s="14" t="n">
         <f aca="false">H10+H15+H17+H22</f>
-        <v>110400</v>
+        <v>111310.7175534</v>
       </c>
       <c r="I24" s="14" t="n">
         <f aca="false">I10+I15+I17+I22</f>
-        <v>158068.276666667</v>
+        <v>212060.009005555</v>
       </c>
       <c r="J24" s="14" t="n">
         <f aca="false">J10+J15+J17+J22</f>
-        <v>226364.493333333</v>
+        <v>334059.221125596</v>
       </c>
       <c r="K24" s="14" t="n">
         <f aca="false">K10+K15+K17+K22</f>
-        <v>349188.934</v>
+        <v>491549.725974113</v>
       </c>
       <c r="L24" s="14" t="n">
         <f aca="false">L10+L15+L17+L22</f>
-        <v>514276.457333333</v>
+        <v>637024.692639584</v>
       </c>
       <c r="M24" s="14" t="n">
         <f aca="false">M10+M15+M17+M22</f>
-        <v>739856.214666667</v>
+        <v>822998.676497369</v>
       </c>
       <c r="N24" s="14" t="n">
         <f aca="false">N10+N15+N17+N22</f>
-        <v>1052000</v>
+        <v>1052002.20443021</v>
       </c>
       <c r="O24" s="14" t="n">
         <f aca="false">O10+O15+O17+O22</f>
-        <v>1310372.16766667</v>
+        <v>1363874.94943339</v>
       </c>
       <c r="P24" s="14" t="n">
         <f aca="false">P10+P15+P17+P22</f>
-        <v>1630607.383</v>
+        <v>1728922.29224888</v>
       </c>
       <c r="Q24" s="14" t="n">
         <f aca="false">Q10+Q15+Q17+Q22</f>
-        <v>2027653.75</v>
+        <v>2150777.55622092</v>
       </c>
       <c r="R24" s="14" t="n">
         <f aca="false">R10+R15+R17+R22</f>
-        <v>2522023.84433333</v>
+        <v>2653542.47171659</v>
       </c>
       <c r="S24" s="14" t="n">
         <f aca="false">S10+S15+S17+S22</f>
-        <v>3136716.121</v>
+        <v>3239143.09230418</v>
       </c>
       <c r="T24" s="14" t="n">
         <f aca="false">T10+T15+T17+T22</f>
-        <v>3902000</v>
+        <v>3909623.66282134</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2454,63 +2491,63 @@
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">(F10-F9*Рычаги!$B$9+F15+F22)*12</f>
-        <v>36115.2</v>
+        <v>58661.856</v>
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">(G10-G9*Рычаги!$B$9+G15+G22)*12</f>
-        <v>67368.96</v>
+        <v>122595.53472</v>
       </c>
       <c r="H25" s="14" t="n">
         <f aca="false">(H10-H9*Рычаги!$B$9+H15+H22)*12</f>
-        <v>724800</v>
+        <v>735728.6106408</v>
       </c>
       <c r="I25" s="14" t="n">
         <f aca="false">(I10-I9*Рычаги!$B$9+I15+I22)*12</f>
-        <v>1140879.32</v>
+        <v>1344720.10806666</v>
       </c>
       <c r="J25" s="14" t="n">
         <f aca="false">(J10-J9*Рычаги!$B$9+J15+J22)*12</f>
-        <v>1763933.92</v>
+        <v>2208710.65350715</v>
       </c>
       <c r="K25" s="14" t="n">
         <f aca="false">(K10-K9*Рычаги!$B$9+K15+K22)*12</f>
-        <v>2990267.208</v>
+        <v>3498596.71168936</v>
       </c>
       <c r="L25" s="14" t="n">
         <f aca="false">(L10-L9*Рычаги!$B$9+L15+L22)*12</f>
-        <v>4659437.488</v>
+        <v>5244296.31167501</v>
       </c>
       <c r="M25" s="14" t="n">
         <f aca="false">(M10-M9*Рычаги!$B$9+M15+M22)*12</f>
-        <v>6973394.576</v>
+        <v>7475984.11796843</v>
       </c>
       <c r="N25" s="14" t="n">
         <f aca="false">(N10-N9*Рычаги!$B$9+N15+N22)*12</f>
-        <v>10224000</v>
+        <v>10224026.4531626</v>
       </c>
       <c r="O25" s="14" t="n">
         <f aca="false">(O10-O9*Рычаги!$B$9+O15+O22)*12</f>
-        <v>13030586.012</v>
+        <v>13566479.3932007</v>
       </c>
       <c r="P25" s="14" t="n">
         <f aca="false">(P10-P9*Рычаги!$B$9+P15+P22)*12</f>
-        <v>16543468.596</v>
+        <v>17547087.5069866</v>
       </c>
       <c r="Q25" s="14" t="n">
         <f aca="false">(Q10-Q9*Рычаги!$B$9+Q15+Q22)*12</f>
-        <v>20937705</v>
+        <v>22209330.674651</v>
       </c>
       <c r="R25" s="14" t="n">
         <f aca="false">(R10-R9*Рычаги!$B$9+R15+R22)*12</f>
-        <v>26454526.132</v>
+        <v>27842489.660599</v>
       </c>
       <c r="S25" s="14" t="n">
         <f aca="false">(S10-S9*Рычаги!$B$9+S15+S22)*12</f>
-        <v>33364273.452</v>
+        <v>34469737.1076502</v>
       </c>
       <c r="T25" s="14" t="n">
         <f aca="false">(T10-T9*Рычаги!$B$9+T15+T22)*12</f>
-        <v>42024000</v>
+        <v>42115483.953856</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2544,58 +2581,58 @@
       <c r="B27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="12" t="n">
-        <v>17.3205</v>
-      </c>
-      <c r="E27" s="12" t="n">
+      <c r="D27" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>36.7171</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>44.9382</v>
-      </c>
-      <c r="H27" s="12" t="n">
+      <c r="F27" s="15" t="n">
+        <v>38.3333</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>46.6667</v>
+      </c>
+      <c r="H27" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>60.2453</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>65.9907</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>72.2842</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>79.1778</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>86.7288</v>
-      </c>
-      <c r="N27" s="12" t="n">
+      <c r="I27" s="15" t="n">
+        <v>61.6667</v>
+      </c>
+      <c r="J27" s="15" t="n">
+        <v>68.3333</v>
+      </c>
+      <c r="K27" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="L27" s="15" t="n">
+        <v>81.6667</v>
+      </c>
+      <c r="M27" s="15" t="n">
+        <v>88.3333</v>
+      </c>
+      <c r="N27" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="O27" s="12" t="n">
-        <v>100.73</v>
-      </c>
-      <c r="P27" s="12" t="n">
-        <v>106.8055</v>
-      </c>
-      <c r="Q27" s="12" t="n">
-        <v>113.2475</v>
-      </c>
-      <c r="R27" s="12" t="n">
-        <v>120.0781</v>
-      </c>
-      <c r="S27" s="12" t="n">
-        <v>127.3206</v>
-      </c>
-      <c r="T27" s="12" t="n">
+      <c r="O27" s="15" t="n">
+        <v>101.6667</v>
+      </c>
+      <c r="P27" s="15" t="n">
+        <v>108.3333</v>
+      </c>
+      <c r="Q27" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="R27" s="15" t="n">
+        <v>121.6667</v>
+      </c>
+      <c r="S27" s="15" t="n">
+        <v>128.3333</v>
+      </c>
+      <c r="T27" s="15" t="n">
         <v>135</v>
       </c>
     </row>
@@ -2612,7 +2649,7 @@
       </c>
       <c r="D28" s="14" t="n">
         <f aca="false">D27*Рычаги!$B$21/12</f>
-        <v>216506.25</v>
+        <v>250000</v>
       </c>
       <c r="E28" s="14" t="n">
         <f aca="false">E27*Рычаги!$B$21/12</f>
@@ -2620,11 +2657,11 @@
       </c>
       <c r="F28" s="14" t="n">
         <f aca="false">F27*Рычаги!$B$21/12</f>
-        <v>458963.75</v>
+        <v>479166.25</v>
       </c>
       <c r="G28" s="14" t="n">
         <f aca="false">G27*Рычаги!$B$21/12</f>
-        <v>561727.5</v>
+        <v>583333.75</v>
       </c>
       <c r="H28" s="14" t="n">
         <f aca="false">H27*Рычаги!$B$21/12</f>
@@ -2632,23 +2669,23 @@
       </c>
       <c r="I28" s="14" t="n">
         <f aca="false">I27*Рычаги!$B$21/12</f>
-        <v>753066.25</v>
+        <v>770833.75</v>
       </c>
       <c r="J28" s="14" t="n">
         <f aca="false">J27*Рычаги!$B$21/12</f>
-        <v>824883.75</v>
+        <v>854166.25</v>
       </c>
       <c r="K28" s="14" t="n">
         <f aca="false">K27*Рычаги!$B$21/12</f>
-        <v>903552.5</v>
+        <v>937500</v>
       </c>
       <c r="L28" s="14" t="n">
         <f aca="false">L27*Рычаги!$B$21/12</f>
-        <v>989722.5</v>
+        <v>1020833.75</v>
       </c>
       <c r="M28" s="14" t="n">
         <f aca="false">M27*Рычаги!$B$21/12</f>
-        <v>1084110</v>
+        <v>1104166.25</v>
       </c>
       <c r="N28" s="14" t="n">
         <f aca="false">N27*Рычаги!$B$21/12</f>
@@ -2656,23 +2693,23 @@
       </c>
       <c r="O28" s="14" t="n">
         <f aca="false">O27*Рычаги!$B$21/12</f>
-        <v>1259125</v>
+        <v>1270833.75</v>
       </c>
       <c r="P28" s="14" t="n">
         <f aca="false">P27*Рычаги!$B$21/12</f>
-        <v>1335068.75</v>
+        <v>1354166.25</v>
       </c>
       <c r="Q28" s="14" t="n">
         <f aca="false">Q27*Рычаги!$B$21/12</f>
-        <v>1415593.75</v>
+        <v>1437500</v>
       </c>
       <c r="R28" s="14" t="n">
         <f aca="false">R27*Рычаги!$B$21/12</f>
-        <v>1500976.25</v>
+        <v>1520833.75</v>
       </c>
       <c r="S28" s="14" t="n">
         <f aca="false">S27*Рычаги!$B$21/12</f>
-        <v>1591507.5</v>
+        <v>1604166.25</v>
       </c>
       <c r="T28" s="14" t="n">
         <f aca="false">T27*Рычаги!$B$21/12</f>
@@ -2686,58 +2723,58 @@
       <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="18" t="n">
         <v>803833.3333</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="18" t="n">
         <v>1236666.6667</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="18" t="n">
         <v>1669500</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="18" t="n">
         <v>1669500</v>
       </c>
-      <c r="G29" s="16" t="n">
+      <c r="G29" s="18" t="n">
         <v>1900000</v>
       </c>
-      <c r="H29" s="16" t="n">
+      <c r="H29" s="18" t="n">
         <v>2130500</v>
       </c>
-      <c r="I29" s="16" t="n">
+      <c r="I29" s="18" t="n">
         <v>2130500</v>
       </c>
-      <c r="J29" s="16" t="n">
+      <c r="J29" s="18" t="n">
         <v>2224966.6667</v>
       </c>
-      <c r="K29" s="16" t="n">
+      <c r="K29" s="18" t="n">
         <v>2319433.3333</v>
       </c>
-      <c r="L29" s="16" t="n">
+      <c r="L29" s="18" t="n">
         <v>2413900</v>
       </c>
-      <c r="M29" s="16" t="n">
+      <c r="M29" s="18" t="n">
         <v>2508366.6667</v>
       </c>
-      <c r="N29" s="16" t="n">
+      <c r="N29" s="18" t="n">
         <v>2602833.3333</v>
       </c>
-      <c r="O29" s="16" t="n">
+      <c r="O29" s="18" t="n">
         <v>2602833.3333</v>
       </c>
-      <c r="P29" s="16" t="n">
+      <c r="P29" s="18" t="n">
         <v>2788366.6667</v>
       </c>
-      <c r="Q29" s="16" t="n">
+      <c r="Q29" s="18" t="n">
         <v>2973900</v>
       </c>
-      <c r="R29" s="16" t="n">
+      <c r="R29" s="18" t="n">
         <v>3159433.3333</v>
       </c>
-      <c r="S29" s="16" t="n">
+      <c r="S29" s="18" t="n">
         <v>3344966.6667</v>
       </c>
-      <c r="T29" s="16" t="n">
+      <c r="T29" s="18" t="n">
         <v>3530500</v>
       </c>
     </row>
@@ -2754,7 +2791,7 @@
       </c>
       <c r="D30" s="14" t="n">
         <f aca="false">D29-D28</f>
-        <v>1020160.4167</v>
+        <v>986666.6667</v>
       </c>
       <c r="E30" s="14" t="n">
         <f aca="false">E29-E28</f>
@@ -2762,11 +2799,11 @@
       </c>
       <c r="F30" s="14" t="n">
         <f aca="false">F29-F28</f>
-        <v>1210536.25</v>
+        <v>1190333.75</v>
       </c>
       <c r="G30" s="14" t="n">
         <f aca="false">G29-G28</f>
-        <v>1338272.5</v>
+        <v>1316666.25</v>
       </c>
       <c r="H30" s="14" t="n">
         <f aca="false">H29-H28</f>
@@ -2774,23 +2811,23 @@
       </c>
       <c r="I30" s="14" t="n">
         <f aca="false">I29-I28</f>
-        <v>1377433.75</v>
+        <v>1359666.25</v>
       </c>
       <c r="J30" s="14" t="n">
         <f aca="false">J29-J28</f>
-        <v>1400082.9167</v>
+        <v>1370800.4167</v>
       </c>
       <c r="K30" s="14" t="n">
         <f aca="false">K29-K28</f>
-        <v>1415880.8333</v>
+        <v>1381933.3333</v>
       </c>
       <c r="L30" s="14" t="n">
         <f aca="false">L29-L28</f>
-        <v>1424177.5</v>
+        <v>1393066.25</v>
       </c>
       <c r="M30" s="14" t="n">
         <f aca="false">M29-M28</f>
-        <v>1424256.6667</v>
+        <v>1404200.4167</v>
       </c>
       <c r="N30" s="14" t="n">
         <f aca="false">N29-N28</f>
@@ -2798,23 +2835,23 @@
       </c>
       <c r="O30" s="14" t="n">
         <f aca="false">O29-O28</f>
-        <v>1343708.3333</v>
+        <v>1331999.5833</v>
       </c>
       <c r="P30" s="14" t="n">
         <f aca="false">P29-P28</f>
-        <v>1453297.9167</v>
+        <v>1434200.4167</v>
       </c>
       <c r="Q30" s="14" t="n">
         <f aca="false">Q29-Q28</f>
-        <v>1558306.25</v>
+        <v>1536400</v>
       </c>
       <c r="R30" s="14" t="n">
         <f aca="false">R29-R28</f>
-        <v>1658457.0833</v>
+        <v>1638599.5833</v>
       </c>
       <c r="S30" s="14" t="n">
         <f aca="false">S29-S28</f>
-        <v>1753459.1667</v>
+        <v>1740800.4167</v>
       </c>
       <c r="T30" s="14" t="n">
         <f aca="false">T29-T28</f>
@@ -2822,7 +2859,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="16" t="s">
         <v>69</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -2842,67 +2879,67 @@
       </c>
       <c r="F31" s="14" t="n">
         <f aca="false">F24-F29</f>
-        <v>-1608490.4</v>
+        <v>-1606611.512</v>
       </c>
       <c r="G31" s="14" t="n">
         <f aca="false">G24-G29</f>
-        <v>-1836385.92</v>
+        <v>-1831783.70544</v>
       </c>
       <c r="H31" s="14" t="n">
         <f aca="false">H24-H29</f>
-        <v>-2020100</v>
+        <v>-2019189.2824466</v>
       </c>
       <c r="I31" s="14" t="n">
         <f aca="false">I24-I29</f>
-        <v>-1972431.72333333</v>
+        <v>-1918439.99099444</v>
       </c>
       <c r="J31" s="14" t="n">
         <f aca="false">J24-J29</f>
-        <v>-1998602.17336667</v>
+        <v>-1890907.4455744</v>
       </c>
       <c r="K31" s="14" t="n">
         <f aca="false">K24-K29</f>
-        <v>-1970244.3993</v>
+        <v>-1827883.60732589</v>
       </c>
       <c r="L31" s="14" t="n">
         <f aca="false">L24-L29</f>
-        <v>-1899623.54266667</v>
+        <v>-1776875.30736042</v>
       </c>
       <c r="M31" s="14" t="n">
         <f aca="false">M24-M29</f>
-        <v>-1768510.45203333</v>
+        <v>-1685367.99020263</v>
       </c>
       <c r="N31" s="14" t="n">
         <f aca="false">N24-N29</f>
-        <v>-1550833.3333</v>
+        <v>-1550831.12886979</v>
       </c>
       <c r="O31" s="14" t="n">
         <f aca="false">O24-O29</f>
-        <v>-1292461.16563333</v>
+        <v>-1238958.38386661</v>
       </c>
       <c r="P31" s="14" t="n">
         <f aca="false">P24-P29</f>
-        <v>-1157759.2837</v>
+        <v>-1059444.37445112</v>
       </c>
       <c r="Q31" s="14" t="n">
         <f aca="false">Q24-Q29</f>
-        <v>-946246.25</v>
+        <v>-823122.44377908</v>
       </c>
       <c r="R31" s="14" t="n">
         <f aca="false">R24-R29</f>
-        <v>-637409.488966667</v>
+        <v>-505890.861583414</v>
       </c>
       <c r="S31" s="14" t="n">
         <f aca="false">S24-S29</f>
-        <v>-208250.5457</v>
+        <v>-105823.574395817</v>
       </c>
       <c r="T31" s="14" t="n">
         <f aca="false">T24-T29</f>
-        <v>371500</v>
+        <v>379123.662821335</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="16" t="s">
         <v>70</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -2922,63 +2959,116 @@
       </c>
       <c r="F32" s="14" t="n">
         <f aca="false">E32+F31</f>
-        <v>44745109.6</v>
+        <v>44746988.488</v>
       </c>
       <c r="G32" s="14" t="n">
         <f aca="false">F32+G31</f>
-        <v>42908723.68</v>
+        <v>42915204.78256</v>
       </c>
       <c r="H32" s="14" t="n">
         <f aca="false">G32+H31</f>
-        <v>40888623.68</v>
+        <v>40896015.5001134</v>
       </c>
       <c r="I32" s="14" t="n">
         <f aca="false">H32+I31</f>
-        <v>38916191.9566667</v>
+        <v>38977575.509119</v>
       </c>
       <c r="J32" s="14" t="n">
         <f aca="false">I32+J31</f>
-        <v>36917589.7833</v>
+        <v>37086668.0635446</v>
       </c>
       <c r="K32" s="14" t="n">
         <f aca="false">J32+K31</f>
-        <v>34947345.384</v>
+        <v>35258784.4562187</v>
       </c>
       <c r="L32" s="14" t="n">
         <f aca="false">K32+L31</f>
-        <v>33047721.8413333</v>
+        <v>33481909.1488582</v>
       </c>
       <c r="M32" s="14" t="n">
         <f aca="false">L32+M31</f>
-        <v>31279211.3893</v>
+        <v>31796541.1586556</v>
       </c>
       <c r="N32" s="14" t="n">
         <f aca="false">M32+N31</f>
-        <v>29728378.056</v>
+        <v>30245710.0297858</v>
       </c>
       <c r="O32" s="14" t="n">
         <f aca="false">N32+O31</f>
-        <v>28435916.8903667</v>
+        <v>29006751.6459192</v>
       </c>
       <c r="P32" s="14" t="n">
         <f aca="false">O32+P31</f>
-        <v>27278157.6066667</v>
+        <v>27947307.2714681</v>
       </c>
       <c r="Q32" s="14" t="n">
         <f aca="false">P32+Q31</f>
-        <v>26331911.3566667</v>
+        <v>27124184.827689</v>
       </c>
       <c r="R32" s="14" t="n">
         <f aca="false">Q32+R31</f>
-        <v>25694501.8677</v>
+        <v>26618293.9661056</v>
       </c>
       <c r="S32" s="14" t="n">
         <f aca="false">R32+S31</f>
-        <v>25486251.322</v>
+        <v>26512470.3917098</v>
       </c>
       <c r="T32" s="14" t="n">
         <f aca="false">S32+T31</f>
-        <v>25857751.322</v>
+        <v>26891594.0545311</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <f aca="false">SUM(C29:E29)-Рычаги!$B$24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <f aca="false">SUM(F29:H29)-Рычаги!$B$25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <f aca="false">SUM(I29:N29)-Рычаги!$B$26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <f aca="false">SUM(O29:T29)-Рычаги!$B$27</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2997,7 +3087,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -3006,191 +3096,255 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>77</v>
+      <c r="A5" s="19" t="s">
+        <v>82</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>42000000</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="20" t="n">
         <f aca="false">Модель!T25</f>
-        <v>42024000</v>
-      </c>
-      <c r="D5" s="19" t="str">
+        <v>42115483.953856</v>
+      </c>
+      <c r="D5" s="21" t="str">
         <f aca="false">IF(ABS(C5-B5)&lt;=1500000,"да","НЕТ")</f>
         <v>да</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>78</v>
+      <c r="A6" s="19" t="s">
+        <v>83</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>3600000</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="20" t="n">
+        <f aca="false">Модель!T24-Модель!T17</f>
+        <v>3509623.66282134</v>
+      </c>
+      <c r="D6" s="21" t="str">
+        <f aca="false">IF(ABS(C6-B6)&lt;=300000,"да","НЕТ")</f>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="C7" s="20" t="n">
         <f aca="false">Модель!T24</f>
-        <v>3902000</v>
-      </c>
-      <c r="D6" s="19" t="str">
-        <f aca="false">IF(ABS(C6-B6)&lt;=400000,"да","НЕТ")</f>
-        <v>да</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="6" t="n">
+        <v>3909623.66282134</v>
+      </c>
+      <c r="D7" s="21" t="str">
+        <f aca="false">IF(ABS(C7-B7)&lt;=300000,"да","НЕТ")</f>
+        <v>НЕТ</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>4000000</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C8" s="20" t="n">
         <f aca="false">Модель!T29</f>
         <v>3530500</v>
       </c>
-      <c r="D7" s="19" t="str">
-        <f aca="false">IF(ABS(C7-B7)&lt;=400000,"да","НЕТ")</f>
-        <v>НЕТ</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>-350000</v>
-      </c>
-      <c r="C8" s="18" t="n">
-        <f aca="false">Модель!T31</f>
-        <v>371500</v>
-      </c>
-      <c r="D8" s="19" t="str">
+      <c r="D8" s="21" t="str">
         <f aca="false">IF(ABS(C8-B8)&lt;=300000,"да","НЕТ")</f>
         <v>НЕТ</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>81</v>
+      <c r="A9" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="B9" s="6" t="n">
+        <v>-350000</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <f aca="false">Модель!T31</f>
+        <v>379123.662821335</v>
+      </c>
+      <c r="D9" s="21" t="str">
+        <f aca="false">IF(ABS(C9-B9)&lt;=300000,"да","НЕТ")</f>
+        <v>НЕТ</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>21000000</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C10" s="20" t="n">
         <f aca="false">Модель!T32</f>
-        <v>25857751.322</v>
-      </c>
-      <c r="D9" s="19" t="str">
-        <f aca="false">IF(ABS(C9-B9)&lt;=2000000,"да","НЕТ")</f>
+        <v>26891594.0545311</v>
+      </c>
+      <c r="D10" s="21" t="str">
+        <f aca="false">IF(ABS(C10-B10)&lt;=2000000,"да","НЕТ")</f>
         <v>НЕТ</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" s="8" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <f aca="false">Модель!H7</f>
+        <v>8.67671358</v>
+      </c>
+      <c r="D11" s="21" t="str">
+        <f aca="false">IF(C11&gt;=B11*0.85,"да","НЕТ")</f>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <f aca="false">Модель!Q7</f>
+        <v>102.799487817802</v>
+      </c>
+      <c r="D12" s="21" t="str">
+        <f aca="false">IF(C12&gt;=B12*0.85,"да","НЕТ")</f>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="8" t="n">
         <v>157</v>
       </c>
-      <c r="C10" s="20" t="n">
-        <f aca="false">Модель!T6</f>
-        <v>157</v>
-      </c>
-      <c r="D10" s="19" t="str">
-        <f aca="false">IF(ABS(C10-B10)&lt;=5,"да","НЕТ")</f>
+      <c r="C13" s="22" t="n">
+        <f aca="false">Модель!T7</f>
+        <v>157.693040230126</v>
+      </c>
+      <c r="D13" s="21" t="str">
+        <f aca="false">IF(ABS(C13-B13)&lt;=5,"да","НЕТ")</f>
         <v>да</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="8" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <f aca="false">Модель!H20</f>
+        <v>17.2376438975</v>
+      </c>
+      <c r="D14" s="21" t="str">
+        <f aca="false">IF(C14&gt;=B14*0.85,"да","НЕТ")</f>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <f aca="false">Модель!Q20</f>
+        <v>179.422703690869</v>
+      </c>
+      <c r="D15" s="21" t="str">
+        <f aca="false">IF(C15&gt;=B15*0.85,"да","НЕТ")</f>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>256</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <f aca="false">Модель!T20</f>
+        <v>292.264936305647</v>
+      </c>
+      <c r="D16" s="21" t="str">
+        <f aca="false">IF(ABS(C16-B16)&lt;=10,"да","НЕТ")</f>
+        <v>НЕТ</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="8" t="n">
         <v>63500</v>
       </c>
-      <c r="C11" s="20" t="n">
-        <f aca="false">Модель!T12</f>
-        <v>63500</v>
-      </c>
-      <c r="D11" s="19" t="str">
-        <f aca="false">IF(ABS(C11-B11)&lt;=2000,"да","НЕТ")</f>
-        <v>да</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>256</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <f aca="false">Модель!T19</f>
-        <v>256</v>
-      </c>
-      <c r="D12" s="19" t="str">
-        <f aca="false">IF(ABS(C12-B12)&lt;=10,"да","НЕТ")</f>
-        <v>да</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="C13" s="20" t="n">
+      <c r="C17" s="22" t="n">
         <f aca="false">Модель!T14</f>
-        <v>2068292.6484</v>
-      </c>
-      <c r="D13" s="19" t="str">
-        <f aca="false">IF(ABS(C13-B13)&lt;=300000,"да","НЕТ")</f>
+        <v>55969.8186758158</v>
+      </c>
+      <c r="D17" s="21" t="str">
+        <f aca="false">IF(ABS(C17-B17)&lt;=2000,"да","НЕТ")</f>
         <v>НЕТ</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="8" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="8" t="n">
         <v>135</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C18" s="22" t="n">
         <f aca="false">Модель!T27</f>
         <v>135</v>
       </c>
-      <c r="D14" s="19" t="str">
-        <f aca="false">IF(ABS(C14-B14)&lt;=5,"да","НЕТ")</f>
+      <c r="D18" s="21" t="str">
+        <f aca="false">IF(ABS(C18-B18)&lt;=5,"да","НЕТ")</f>
         <v>да</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>87</v>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/strategy/finmodel-wif.xlsx
+++ b/strategy/finmodel-wif.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Модель по месяцам · базовый сценарий</t>
   </si>
   <si>
-    <t xml:space="preserve">Синие строки — вводные: поток новых клиентов (план продаж), визиты, штат, расход. Всё остальное — формулы: база = прошлый месяц × (1 − отток) + новые. Поменяй поток или отток — пересчитается выручка, касса и проверки.</t>
+    <t xml:space="preserve">Синие строки — вводные: поток новых клиентов (план продаж), визиты, штат, расход. Всё остальное — формулы: база = прошлый месяц − ROUND(прошлый × отток) + новые, все штуки целые. Поменяй поток или отток — пересчитается выручка, касса и проверки.</t>
   </si>
   <si>
     <t xml:space="preserve">Месяц</t>
@@ -319,13 +319,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0"/>
+    <numFmt numFmtId="168" formatCode="#,##0"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -470,7 +469,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -519,19 +518,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1225,46 +1220,46 @@
         <v>0</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>1.4558</v>
+        <v>2</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>2.9116</v>
+        <v>3</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>4.3674</v>
+        <v>5</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>5.6395</v>
+        <v>5</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>6.9116</v>
+        <v>6</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>8.1837</v>
+        <v>7</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>9.4558</v>
+        <v>9</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>10.7279</v>
+        <v>11</v>
       </c>
       <c r="N6" s="12" t="n">
         <v>12</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>15</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="R6" s="12" t="n">
         <v>18</v>
       </c>
       <c r="S6" s="12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="T6" s="12" t="n">
         <v>21</v>
@@ -1282,72 +1277,72 @@
         <v>0</v>
       </c>
       <c r="D7" s="13" t="n">
-        <f aca="false">C7*(1-Рычаги!$B$8)+D6</f>
+        <f aca="false">C7-ROUND(C7*Рычаги!$B$8,0)+D6</f>
         <v>0</v>
       </c>
       <c r="E7" s="13" t="n">
-        <f aca="false">D7*(1-Рычаги!$B$8)+E6</f>
+        <f aca="false">D7-ROUND(D7*Рычаги!$B$8,0)+E6</f>
         <v>0</v>
       </c>
       <c r="F7" s="13" t="n">
-        <f aca="false">E7*(1-Рычаги!$B$8)+F6</f>
-        <v>1.4558</v>
+        <f aca="false">E7-ROUND(E7*Рычаги!$B$8,0)+F6</f>
+        <v>2</v>
       </c>
       <c r="G7" s="13" t="n">
-        <f aca="false">F7*(1-Рычаги!$B$8)+G6</f>
-        <v>4.352842</v>
+        <f aca="false">F7-ROUND(F7*Рычаги!$B$8,0)+G6</f>
+        <v>5</v>
       </c>
       <c r="H7" s="13" t="n">
-        <f aca="false">G7*(1-Рычаги!$B$8)+H6</f>
-        <v>8.67671358</v>
+        <f aca="false">G7-ROUND(G7*Рычаги!$B$8,0)+H6</f>
+        <v>10</v>
       </c>
       <c r="I7" s="13" t="n">
-        <f aca="false">H7*(1-Рычаги!$B$8)+I6</f>
-        <v>14.2294464442</v>
+        <f aca="false">H7-ROUND(H7*Рычаги!$B$8,0)+I6</f>
+        <v>15</v>
       </c>
       <c r="J7" s="13" t="n">
-        <f aca="false">I7*(1-Рычаги!$B$8)+J6</f>
-        <v>20.998751979758</v>
+        <f aca="false">I7-ROUND(I7*Рычаги!$B$8,0)+J6</f>
+        <v>21</v>
       </c>
       <c r="K7" s="13" t="n">
-        <f aca="false">J7*(1-Рычаги!$B$8)+K6</f>
-        <v>28.9724644599604</v>
+        <f aca="false">J7-ROUND(J7*Рычаги!$B$8,0)+K6</f>
+        <v>28</v>
       </c>
       <c r="L7" s="13" t="n">
-        <f aca="false">K7*(1-Рычаги!$B$8)+L6</f>
-        <v>38.1385398153608</v>
+        <f aca="false">K7-ROUND(K7*Рычаги!$B$8,0)+L6</f>
+        <v>37</v>
       </c>
       <c r="M7" s="13" t="n">
-        <f aca="false">L7*(1-Рычаги!$B$8)+M6</f>
-        <v>48.4850544172072</v>
+        <f aca="false">L7-ROUND(L7*Рычаги!$B$8,0)+M6</f>
+        <v>48</v>
       </c>
       <c r="N7" s="13" t="n">
-        <f aca="false">M7*(1-Рычаги!$B$8)+N6</f>
-        <v>60.0002038730351</v>
+        <f aca="false">M7-ROUND(M7*Рычаги!$B$8,0)+N6</f>
+        <v>60</v>
       </c>
       <c r="O7" s="13" t="n">
-        <f aca="false">N7*(1-Рычаги!$B$8)+O6</f>
-        <v>72.9002018343048</v>
+        <f aca="false">N7-ROUND(N7*Рычаги!$B$8,0)+O6</f>
+        <v>73</v>
       </c>
       <c r="P7" s="13" t="n">
-        <f aca="false">O7*(1-Рычаги!$B$8)+P6</f>
-        <v>87.1711998159617</v>
+        <f aca="false">O7-ROUND(O7*Рычаги!$B$8,0)+P6</f>
+        <v>87</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <f aca="false">P7*(1-Рычаги!$B$8)+Q6</f>
-        <v>102.799487817802</v>
+        <f aca="false">P7-ROUND(P7*Рычаги!$B$8,0)+Q6</f>
+        <v>103</v>
       </c>
       <c r="R7" s="13" t="n">
-        <f aca="false">Q7*(1-Рычаги!$B$8)+R6</f>
-        <v>119.771492939624</v>
+        <f aca="false">Q7-ROUND(Q7*Рычаги!$B$8,0)+R6</f>
+        <v>120</v>
       </c>
       <c r="S7" s="13" t="n">
-        <f aca="false">R7*(1-Рычаги!$B$8)+S6</f>
-        <v>138.073778010228</v>
+        <f aca="false">R7-ROUND(R7*Рычаги!$B$8,0)+S6</f>
+        <v>139</v>
       </c>
       <c r="T7" s="13" t="n">
-        <f aca="false">S7*(1-Рычаги!$B$8)+T6</f>
-        <v>157.693040230126</v>
+        <f aca="false">S7-ROUND(S7*Рычаги!$B$8,0)+T6</f>
+        <v>159</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1437,63 +1432,63 @@
       <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="15" t="n">
+      <c r="C9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="15" t="n">
+      <c r="H9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="15" t="s">
         <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1521,55 +1516,55 @@
       </c>
       <c r="H10" s="14" t="n">
         <f aca="false">H7*H8+H9*Рычаги!$B$9</f>
-        <v>43383.5679</v>
+        <v>50000</v>
       </c>
       <c r="I10" s="14" t="n">
         <f aca="false">I7*I8+I9*Рычаги!$B$9</f>
-        <v>83005.1042578333</v>
+        <v>87500</v>
       </c>
       <c r="J10" s="14" t="n">
         <f aca="false">J7*J8+J9*Рычаги!$B$9</f>
-        <v>139991.679865053</v>
+        <v>140000</v>
       </c>
       <c r="K10" s="14" t="n">
         <f aca="false">K7*K8+K9*Рычаги!$B$9</f>
-        <v>217293.483449703</v>
+        <v>210000</v>
       </c>
       <c r="L10" s="14" t="n">
         <f aca="false">L7*L8+L9*Рычаги!$B$9</f>
-        <v>317821.165128007</v>
+        <v>308333.333333333</v>
       </c>
       <c r="M10" s="14" t="n">
         <f aca="false">M7*M8+M9*Рычаги!$B$9</f>
-        <v>444446.332157733</v>
+        <v>440000</v>
       </c>
       <c r="N10" s="14" t="n">
         <f aca="false">N7*N8+N9*Рычаги!$B$9</f>
-        <v>600002.038730351</v>
+        <v>600000</v>
       </c>
       <c r="O10" s="14" t="n">
         <f aca="false">O7*O8+O9*Рычаги!$B$9</f>
-        <v>789752.186538302</v>
+        <v>790833.333333333</v>
       </c>
       <c r="P10" s="14" t="n">
         <f aca="false">P7*P8+P9*Рычаги!$B$9</f>
-        <v>1016997.33118622</v>
+        <v>1015000</v>
       </c>
       <c r="Q10" s="14" t="n">
         <f aca="false">Q7*Q8+Q9*Рычаги!$B$9</f>
-        <v>1284993.59772253</v>
+        <v>1287500</v>
       </c>
       <c r="R10" s="14" t="n">
         <f aca="false">R7*R8+R9*Рычаги!$B$9</f>
-        <v>1596953.23919499</v>
+        <v>1600000</v>
       </c>
       <c r="S10" s="14" t="n">
         <f aca="false">S7*S8+S9*Рычаги!$B$9</f>
-        <v>1956045.18847823</v>
+        <v>1969166.66666667</v>
       </c>
       <c r="T10" s="14" t="n">
         <f aca="false">T7*T8+T9*Рычаги!$B$9</f>
-        <v>2365395.60345188</v>
+        <v>2385000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1603,58 +1598,58 @@
       <c r="B12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>108324.8984</v>
-      </c>
-      <c r="L12" s="15" t="n">
-        <v>216649.7969</v>
-      </c>
-      <c r="M12" s="15" t="n">
-        <v>324974.6953</v>
-      </c>
-      <c r="N12" s="15" t="n">
-        <v>433299.5937</v>
-      </c>
-      <c r="O12" s="15" t="n">
-        <v>525208.7109</v>
-      </c>
-      <c r="P12" s="15" t="n">
-        <v>617117.8281</v>
-      </c>
-      <c r="Q12" s="15" t="n">
-        <v>709026.9453</v>
-      </c>
-      <c r="R12" s="15" t="n">
-        <v>1006017.9635</v>
-      </c>
-      <c r="S12" s="15" t="n">
-        <v>1303008.9818</v>
-      </c>
-      <c r="T12" s="15" t="n">
+      <c r="C12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>108325</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>216650</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>324975</v>
+      </c>
+      <c r="N12" s="12" t="n">
+        <v>433300</v>
+      </c>
+      <c r="O12" s="12" t="n">
+        <v>525183</v>
+      </c>
+      <c r="P12" s="12" t="n">
+        <v>617067</v>
+      </c>
+      <c r="Q12" s="12" t="n">
+        <v>708950</v>
+      </c>
+      <c r="R12" s="12" t="n">
+        <v>1005967</v>
+      </c>
+      <c r="S12" s="12" t="n">
+        <v>1302983</v>
+      </c>
+      <c r="T12" s="12" t="n">
         <v>1600000</v>
       </c>
     </row>
@@ -1665,76 +1660,76 @@
       <c r="B13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="17" t="n">
-        <f aca="false">C12*Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <f aca="false">D12*Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <f aca="false">E12*Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <f aca="false">F12*Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <f aca="false">G12*Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <f aca="false">H12*Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <f aca="false">I12*Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <f aca="false">J12*Рычаги!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <f aca="false">K12*Рычаги!$B$14</f>
-        <v>1083.248984</v>
-      </c>
-      <c r="L13" s="17" t="n">
-        <f aca="false">L12*Рычаги!$B$14</f>
-        <v>2166.497969</v>
-      </c>
-      <c r="M13" s="17" t="n">
-        <f aca="false">M12*Рычаги!$B$14</f>
-        <v>3249.746953</v>
-      </c>
-      <c r="N13" s="17" t="n">
-        <f aca="false">N12*Рычаги!$B$14</f>
-        <v>4332.995937</v>
-      </c>
-      <c r="O13" s="17" t="n">
-        <f aca="false">O12*Рычаги!$B$14</f>
-        <v>5252.087109</v>
-      </c>
-      <c r="P13" s="17" t="n">
-        <f aca="false">P12*Рычаги!$B$14</f>
-        <v>6171.178281</v>
-      </c>
-      <c r="Q13" s="17" t="n">
-        <f aca="false">Q12*Рычаги!$B$14</f>
-        <v>7090.269453</v>
-      </c>
-      <c r="R13" s="17" t="n">
-        <f aca="false">R12*Рычаги!$B$14</f>
-        <v>10060.179635</v>
-      </c>
-      <c r="S13" s="17" t="n">
-        <f aca="false">S12*Рычаги!$B$14</f>
-        <v>13030.089818</v>
-      </c>
-      <c r="T13" s="17" t="n">
-        <f aca="false">T12*Рычаги!$B$14</f>
+      <c r="C13" s="16" t="n">
+        <f aca="false">ROUND(C12*Рычаги!$B$14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">ROUND(D12*Рычаги!$B$14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <f aca="false">ROUND(E12*Рычаги!$B$14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <f aca="false">ROUND(F12*Рычаги!$B$14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <f aca="false">ROUND(G12*Рычаги!$B$14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <f aca="false">ROUND(H12*Рычаги!$B$14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <f aca="false">ROUND(I12*Рычаги!$B$14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="16" t="n">
+        <f aca="false">ROUND(J12*Рычаги!$B$14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <f aca="false">ROUND(K12*Рычаги!$B$14,0)</f>
+        <v>1083</v>
+      </c>
+      <c r="L13" s="16" t="n">
+        <f aca="false">ROUND(L12*Рычаги!$B$14,0)</f>
+        <v>2167</v>
+      </c>
+      <c r="M13" s="16" t="n">
+        <f aca="false">ROUND(M12*Рычаги!$B$14,0)</f>
+        <v>3250</v>
+      </c>
+      <c r="N13" s="16" t="n">
+        <f aca="false">ROUND(N12*Рычаги!$B$14,0)</f>
+        <v>4333</v>
+      </c>
+      <c r="O13" s="16" t="n">
+        <f aca="false">ROUND(O12*Рычаги!$B$14,0)</f>
+        <v>5252</v>
+      </c>
+      <c r="P13" s="16" t="n">
+        <f aca="false">ROUND(P12*Рычаги!$B$14,0)</f>
+        <v>6171</v>
+      </c>
+      <c r="Q13" s="16" t="n">
+        <f aca="false">ROUND(Q12*Рычаги!$B$14,0)</f>
+        <v>7090</v>
+      </c>
+      <c r="R13" s="16" t="n">
+        <f aca="false">ROUND(R12*Рычаги!$B$14,0)</f>
+        <v>10060</v>
+      </c>
+      <c r="S13" s="16" t="n">
+        <f aca="false">ROUND(S12*Рычаги!$B$14,0)</f>
+        <v>13030</v>
+      </c>
+      <c r="T13" s="16" t="n">
+        <f aca="false">ROUND(T12*Рычаги!$B$14,0)</f>
         <v>16000</v>
       </c>
     </row>
@@ -1745,77 +1740,77 @@
       <c r="B14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="16" t="n">
         <f aca="false">C13</f>
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
-        <f aca="false">C14*(1-Рычаги!$B$13)+D13</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <f aca="false">D14*(1-Рычаги!$B$13)+E13</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="17" t="n">
-        <f aca="false">E14*(1-Рычаги!$B$13)+F13</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="17" t="n">
-        <f aca="false">F14*(1-Рычаги!$B$13)+G13</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <f aca="false">G14*(1-Рычаги!$B$13)+H13</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <f aca="false">H14*(1-Рычаги!$B$13)+I13</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <f aca="false">I14*(1-Рычаги!$B$13)+J13</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <f aca="false">J14*(1-Рычаги!$B$13)+K13</f>
-        <v>1083.248984</v>
-      </c>
-      <c r="L14" s="17" t="n">
-        <f aca="false">K14*(1-Рычаги!$B$13)+L13</f>
-        <v>3163.08703428</v>
-      </c>
-      <c r="M14" s="17" t="n">
-        <f aca="false">L14*(1-Рычаги!$B$13)+M13</f>
-        <v>6159.7870245376</v>
-      </c>
-      <c r="N14" s="17" t="n">
-        <f aca="false">M14*(1-Рычаги!$B$13)+N13</f>
-        <v>9999.99999957459</v>
-      </c>
-      <c r="O14" s="17" t="n">
-        <f aca="false">N14*(1-Рычаги!$B$13)+O13</f>
-        <v>14452.0871086086</v>
-      </c>
-      <c r="P14" s="17" t="n">
-        <f aca="false">O14*(1-Рычаги!$B$13)+P13</f>
-        <v>19467.0984209199</v>
-      </c>
-      <c r="Q14" s="17" t="n">
-        <f aca="false">P14*(1-Рычаги!$B$13)+Q13</f>
-        <v>25000.0000002463</v>
-      </c>
-      <c r="R14" s="17" t="n">
-        <f aca="false">Q14*(1-Рычаги!$B$13)+R13</f>
-        <v>33060.1796352266</v>
-      </c>
-      <c r="S14" s="17" t="n">
-        <f aca="false">R14*(1-Рычаги!$B$13)+S13</f>
-        <v>43445.4550824085</v>
-      </c>
-      <c r="T14" s="17" t="n">
-        <f aca="false">S14*(1-Рычаги!$B$13)+T13</f>
-        <v>55969.8186758158</v>
+      <c r="D14" s="16" t="n">
+        <f aca="false">C14-ROUND(C14*Рычаги!$B$13,0)+D13</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <f aca="false">D14-ROUND(D14*Рычаги!$B$13,0)+E13</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <f aca="false">E14-ROUND(E14*Рычаги!$B$13,0)+F13</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <f aca="false">F14-ROUND(F14*Рычаги!$B$13,0)+G13</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <f aca="false">G14-ROUND(G14*Рычаги!$B$13,0)+H13</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <f aca="false">H14-ROUND(H14*Рычаги!$B$13,0)+I13</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="16" t="n">
+        <f aca="false">I14-ROUND(I14*Рычаги!$B$13,0)+J13</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="16" t="n">
+        <f aca="false">J14-ROUND(J14*Рычаги!$B$13,0)+K13</f>
+        <v>1083</v>
+      </c>
+      <c r="L14" s="16" t="n">
+        <f aca="false">K14-ROUND(K14*Рычаги!$B$13,0)+L13</f>
+        <v>3163</v>
+      </c>
+      <c r="M14" s="16" t="n">
+        <f aca="false">L14-ROUND(L14*Рычаги!$B$13,0)+M13</f>
+        <v>6160</v>
+      </c>
+      <c r="N14" s="16" t="n">
+        <f aca="false">M14-ROUND(M14*Рычаги!$B$13,0)+N13</f>
+        <v>10000</v>
+      </c>
+      <c r="O14" s="16" t="n">
+        <f aca="false">N14-ROUND(N14*Рычаги!$B$13,0)+O13</f>
+        <v>14452</v>
+      </c>
+      <c r="P14" s="16" t="n">
+        <f aca="false">O14-ROUND(O14*Рычаги!$B$13,0)+P13</f>
+        <v>19467</v>
+      </c>
+      <c r="Q14" s="16" t="n">
+        <f aca="false">P14-ROUND(P14*Рычаги!$B$13,0)+Q13</f>
+        <v>25000</v>
+      </c>
+      <c r="R14" s="16" t="n">
+        <f aca="false">Q14-ROUND(Q14*Рычаги!$B$13,0)+R13</f>
+        <v>33060</v>
+      </c>
+      <c r="S14" s="16" t="n">
+        <f aca="false">R14-ROUND(R14*Рычаги!$B$13,0)+S13</f>
+        <v>43445</v>
+      </c>
+      <c r="T14" s="16" t="n">
+        <f aca="false">S14-ROUND(S14*Рычаги!$B$13,0)+T13</f>
+        <v>55969</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1859,43 +1854,43 @@
       </c>
       <c r="K15" s="14" t="n">
         <f aca="false">K14*Рычаги!$B$12</f>
-        <v>10832.48984</v>
+        <v>10830</v>
       </c>
       <c r="L15" s="14" t="n">
         <f aca="false">L14*Рычаги!$B$12</f>
-        <v>31630.8703428</v>
+        <v>31630</v>
       </c>
       <c r="M15" s="14" t="n">
         <f aca="false">M14*Рычаги!$B$12</f>
-        <v>61597.870245376</v>
+        <v>61600</v>
       </c>
       <c r="N15" s="14" t="n">
         <f aca="false">N14*Рычаги!$B$12</f>
-        <v>99999.9999957459</v>
+        <v>100000</v>
       </c>
       <c r="O15" s="14" t="n">
         <f aca="false">O14*Рычаги!$B$12</f>
-        <v>144520.871086086</v>
+        <v>144520</v>
       </c>
       <c r="P15" s="14" t="n">
         <f aca="false">P14*Рычаги!$B$12</f>
-        <v>194670.984209199</v>
+        <v>194670</v>
       </c>
       <c r="Q15" s="14" t="n">
         <f aca="false">Q14*Рычаги!$B$12</f>
-        <v>250000.000002463</v>
+        <v>250000</v>
       </c>
       <c r="R15" s="14" t="n">
         <f aca="false">R14*Рычаги!$B$12</f>
-        <v>330601.796352266</v>
+        <v>330600</v>
       </c>
       <c r="S15" s="14" t="n">
         <f aca="false">S14*Рычаги!$B$12</f>
-        <v>434454.550824085</v>
+        <v>434450</v>
       </c>
       <c r="T15" s="14" t="n">
         <f aca="false">T14*Рычаги!$B$12</f>
-        <v>559698.186758158</v>
+        <v>559690</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1942,19 +1937,19 @@
         <v>4</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>4.6667</v>
+        <v>5</v>
       </c>
       <c r="P16" s="12" t="n">
-        <v>5.3333</v>
+        <v>5</v>
       </c>
       <c r="Q16" s="12" t="n">
         <v>6</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>6.6667</v>
+        <v>7</v>
       </c>
       <c r="S16" s="12" t="n">
-        <v>7.3333</v>
+        <v>7</v>
       </c>
       <c r="T16" s="12" t="n">
         <v>8</v>
@@ -2017,11 +2012,11 @@
       </c>
       <c r="O17" s="14" t="n">
         <f aca="false">O16*Рычаги!$B$15</f>
-        <v>233335</v>
+        <v>250000</v>
       </c>
       <c r="P17" s="14" t="n">
         <f aca="false">P16*Рычаги!$B$15</f>
-        <v>266665</v>
+        <v>250000</v>
       </c>
       <c r="Q17" s="14" t="n">
         <f aca="false">Q16*Рычаги!$B$15</f>
@@ -2029,11 +2024,11 @@
       </c>
       <c r="R17" s="14" t="n">
         <f aca="false">R16*Рычаги!$B$15</f>
-        <v>333335</v>
+        <v>350000</v>
       </c>
       <c r="S17" s="14" t="n">
         <f aca="false">S16*Рычаги!$B$15</f>
-        <v>366665</v>
+        <v>350000</v>
       </c>
       <c r="T17" s="14" t="n">
         <f aca="false">T16*Рычаги!$B$15</f>
@@ -2081,46 +2076,46 @@
         <v>2</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>3.5851</v>
+        <v>4</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>5.1702</v>
+        <v>5</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>6.7553</v>
+        <v>6</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>8.9628</v>
+        <v>9</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>11.1702</v>
+        <v>11</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>13.3777</v>
+        <v>13</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>15.5851</v>
+        <v>16</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>17.7926</v>
+        <v>18</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>20</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>24.1667</v>
+        <v>24</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>28.3333</v>
+        <v>28</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>36.6667</v>
+        <v>37</v>
       </c>
       <c r="S19" s="12" t="n">
-        <v>40.8333</v>
+        <v>41</v>
       </c>
       <c r="T19" s="12" t="n">
         <v>45</v>
@@ -2138,72 +2133,72 @@
         <v>0</v>
       </c>
       <c r="D20" s="13" t="n">
-        <f aca="false">C20*(1-Рычаги!$B$19)+D19</f>
+        <f aca="false">C20-ROUND(C20*Рычаги!$B$19,0)+D19</f>
         <v>0</v>
       </c>
       <c r="E20" s="13" t="n">
-        <f aca="false">D20*(1-Рычаги!$B$19)+E19</f>
+        <f aca="false">D20-ROUND(D20*Рычаги!$B$19,0)+E19</f>
         <v>2</v>
       </c>
       <c r="F20" s="13" t="n">
-        <f aca="false">E20*(1-Рычаги!$B$19)+F19</f>
-        <v>5.5551</v>
+        <f aca="false">E20-ROUND(E20*Рычаги!$B$19,0)+F19</f>
+        <v>6</v>
       </c>
       <c r="G20" s="13" t="n">
-        <f aca="false">F20*(1-Рычаги!$B$19)+G19</f>
-        <v>10.6419735</v>
+        <f aca="false">F20-ROUND(F20*Рычаги!$B$19,0)+G19</f>
+        <v>11</v>
       </c>
       <c r="H20" s="13" t="n">
-        <f aca="false">G20*(1-Рычаги!$B$19)+H19</f>
-        <v>17.2376438975</v>
+        <f aca="false">G20-ROUND(G20*Рычаги!$B$19,0)+H19</f>
+        <v>17</v>
       </c>
       <c r="I20" s="13" t="n">
-        <f aca="false">H20*(1-Рычаги!$B$19)+I19</f>
-        <v>25.9418792390375</v>
+        <f aca="false">H20-ROUND(H20*Рычаги!$B$19,0)+I19</f>
+        <v>26</v>
       </c>
       <c r="J20" s="13" t="n">
-        <f aca="false">I20*(1-Рычаги!$B$19)+J19</f>
-        <v>36.7229510504519</v>
+        <f aca="false">I20-ROUND(I20*Рычаги!$B$19,0)+J19</f>
+        <v>37</v>
       </c>
       <c r="K20" s="13" t="n">
-        <f aca="false">J20*(1-Рычаги!$B$19)+K19</f>
-        <v>49.5498067846952</v>
+        <f aca="false">J20-ROUND(J20*Рычаги!$B$19,0)+K19</f>
+        <v>49</v>
       </c>
       <c r="L20" s="13" t="n">
-        <f aca="false">K20*(1-Рычаги!$B$19)+L19</f>
-        <v>64.3916596829247</v>
+        <f aca="false">K20-ROUND(K20*Рычаги!$B$19,0)+L19</f>
+        <v>64</v>
       </c>
       <c r="M20" s="13" t="n">
-        <f aca="false">L20*(1-Рычаги!$B$19)+M19</f>
-        <v>81.2183847876809</v>
+        <f aca="false">L20-ROUND(L20*Рычаги!$B$19,0)+M19</f>
+        <v>81</v>
       </c>
       <c r="N20" s="13" t="n">
-        <f aca="false">M20*(1-Рычаги!$B$19)+N19</f>
-        <v>100.000109015866</v>
+        <f aca="false">M20-ROUND(M20*Рычаги!$B$19,0)+N19</f>
+        <v>100</v>
       </c>
       <c r="O20" s="13" t="n">
-        <f aca="false">N20*(1-Рычаги!$B$19)+O19</f>
-        <v>122.666807380628</v>
+        <f aca="false">N20-ROUND(N20*Рычаги!$B$19,0)+O19</f>
+        <v>122</v>
       </c>
       <c r="P20" s="13" t="n">
-        <f aca="false">O20*(1-Рычаги!$B$19)+P19</f>
-        <v>149.160105269918</v>
+        <f aca="false">O20-ROUND(O20*Рычаги!$B$19,0)+P19</f>
+        <v>148</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <f aca="false">P20*(1-Рычаги!$B$19)+Q19</f>
-        <v>179.422703690869</v>
+        <f aca="false">P20-ROUND(P20*Рычаги!$B$19,0)+Q19</f>
+        <v>179</v>
       </c>
       <c r="R20" s="13" t="n">
-        <f aca="false">Q20*(1-Рычаги!$B$19)+R19</f>
-        <v>213.398063135506</v>
+        <f aca="false">Q20-ROUND(Q20*Рычаги!$B$19,0)+R19</f>
+        <v>213</v>
       </c>
       <c r="S20" s="13" t="n">
-        <f aca="false">R20*(1-Рычаги!$B$19)+S19</f>
-        <v>251.030392188474</v>
+        <f aca="false">R20-ROUND(R20*Рычаги!$B$19,0)+S19</f>
+        <v>251</v>
       </c>
       <c r="T20" s="13" t="n">
-        <f aca="false">S20*(1-Рычаги!$B$19)+T19</f>
-        <v>292.264936305647</v>
+        <f aca="false">S20-ROUND(S20*Рычаги!$B$19,0)+T19</f>
+        <v>292</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2287,7 +2282,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -2307,63 +2302,63 @@
       </c>
       <c r="F22" s="14" t="n">
         <f aca="false">F20*F21</f>
-        <v>4888.488</v>
+        <v>5280</v>
       </c>
       <c r="G22" s="14" t="n">
         <f aca="false">G20*G21</f>
-        <v>10216.29456</v>
+        <v>10560</v>
       </c>
       <c r="H22" s="14" t="n">
         <f aca="false">H20*H21</f>
-        <v>17927.1496534</v>
+        <v>17680</v>
       </c>
       <c r="I22" s="14" t="n">
         <f aca="false">I20*I21</f>
-        <v>29054.904747722</v>
+        <v>29120</v>
       </c>
       <c r="J22" s="14" t="n">
         <f aca="false">J20*J21</f>
-        <v>44067.5412605423</v>
+        <v>44400</v>
       </c>
       <c r="K22" s="14" t="n">
         <f aca="false">K20*K21</f>
-        <v>63423.7526844098</v>
+        <v>62720</v>
       </c>
       <c r="L22" s="14" t="n">
         <f aca="false">L20*L21</f>
-        <v>87572.6571687776</v>
+        <v>87040</v>
       </c>
       <c r="M22" s="14" t="n">
         <f aca="false">M20*M21</f>
-        <v>116954.47409426</v>
+        <v>116640</v>
       </c>
       <c r="N22" s="14" t="n">
         <f aca="false">N20*N21</f>
-        <v>152000.165704116</v>
+        <v>152000</v>
       </c>
       <c r="O22" s="14" t="n">
         <f aca="false">O20*O21</f>
-        <v>196266.891809004</v>
+        <v>195200</v>
       </c>
       <c r="P22" s="14" t="n">
         <f aca="false">P20*P21</f>
-        <v>250588.976853463</v>
+        <v>248640</v>
       </c>
       <c r="Q22" s="14" t="n">
         <f aca="false">Q20*Q21</f>
-        <v>315783.95849593</v>
+        <v>315040</v>
       </c>
       <c r="R22" s="14" t="n">
         <f aca="false">R20*R21</f>
-        <v>392652.436169332</v>
+        <v>391920</v>
       </c>
       <c r="S22" s="14" t="n">
         <f aca="false">S20*S21</f>
-        <v>481978.35300187</v>
+        <v>481920</v>
       </c>
       <c r="T22" s="14" t="n">
         <f aca="false">T20*T21</f>
-        <v>584529.872611294</v>
+        <v>584000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2391,7 +2386,7 @@
       <c r="T23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="15" t="s">
         <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -2411,63 +2406,63 @@
       </c>
       <c r="F24" s="14" t="n">
         <f aca="false">F10+F15+F17+F22</f>
-        <v>62888.488</v>
+        <v>63280</v>
       </c>
       <c r="G24" s="14" t="n">
         <f aca="false">G10+G15+G17+G22</f>
-        <v>68216.29456</v>
+        <v>68560</v>
       </c>
       <c r="H24" s="14" t="n">
         <f aca="false">H10+H15+H17+H22</f>
-        <v>111310.7175534</v>
+        <v>117680</v>
       </c>
       <c r="I24" s="14" t="n">
         <f aca="false">I10+I15+I17+I22</f>
-        <v>212060.009005555</v>
+        <v>216620</v>
       </c>
       <c r="J24" s="14" t="n">
         <f aca="false">J10+J15+J17+J22</f>
-        <v>334059.221125596</v>
+        <v>334400</v>
       </c>
       <c r="K24" s="14" t="n">
         <f aca="false">K10+K15+K17+K22</f>
-        <v>491549.725974113</v>
+        <v>483550</v>
       </c>
       <c r="L24" s="14" t="n">
         <f aca="false">L10+L15+L17+L22</f>
-        <v>637024.692639584</v>
+        <v>627003.333333333</v>
       </c>
       <c r="M24" s="14" t="n">
         <f aca="false">M10+M15+M17+M22</f>
-        <v>822998.676497369</v>
+        <v>818240</v>
       </c>
       <c r="N24" s="14" t="n">
         <f aca="false">N10+N15+N17+N22</f>
-        <v>1052002.20443021</v>
+        <v>1052000</v>
       </c>
       <c r="O24" s="14" t="n">
         <f aca="false">O10+O15+O17+O22</f>
-        <v>1363874.94943339</v>
+        <v>1380553.33333333</v>
       </c>
       <c r="P24" s="14" t="n">
         <f aca="false">P10+P15+P17+P22</f>
-        <v>1728922.29224888</v>
+        <v>1708310</v>
       </c>
       <c r="Q24" s="14" t="n">
         <f aca="false">Q10+Q15+Q17+Q22</f>
-        <v>2150777.55622092</v>
+        <v>2152540</v>
       </c>
       <c r="R24" s="14" t="n">
         <f aca="false">R10+R15+R17+R22</f>
-        <v>2653542.47171659</v>
+        <v>2672520</v>
       </c>
       <c r="S24" s="14" t="n">
         <f aca="false">S10+S15+S17+S22</f>
-        <v>3239143.09230418</v>
+        <v>3235536.66666667</v>
       </c>
       <c r="T24" s="14" t="n">
         <f aca="false">T10+T15+T17+T22</f>
-        <v>3909623.66282134</v>
+        <v>3928690</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2491,63 +2486,63 @@
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">(F10-F9*Рычаги!$B$9+F15+F22)*12</f>
-        <v>58661.856</v>
+        <v>63360</v>
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">(G10-G9*Рычаги!$B$9+G15+G22)*12</f>
-        <v>122595.53472</v>
+        <v>126720</v>
       </c>
       <c r="H25" s="14" t="n">
         <f aca="false">(H10-H9*Рычаги!$B$9+H15+H22)*12</f>
-        <v>735728.6106408</v>
+        <v>812160</v>
       </c>
       <c r="I25" s="14" t="n">
         <f aca="false">(I10-I9*Рычаги!$B$9+I15+I22)*12</f>
-        <v>1344720.10806666</v>
+        <v>1399440</v>
       </c>
       <c r="J25" s="14" t="n">
         <f aca="false">(J10-J9*Рычаги!$B$9+J15+J22)*12</f>
-        <v>2208710.65350715</v>
+        <v>2212800</v>
       </c>
       <c r="K25" s="14" t="n">
         <f aca="false">(K10-K9*Рычаги!$B$9+K15+K22)*12</f>
-        <v>3498596.71168936</v>
+        <v>3402600</v>
       </c>
       <c r="L25" s="14" t="n">
         <f aca="false">(L10-L9*Рычаги!$B$9+L15+L22)*12</f>
-        <v>5244296.31167501</v>
+        <v>5124040</v>
       </c>
       <c r="M25" s="14" t="n">
         <f aca="false">(M10-M9*Рычаги!$B$9+M15+M22)*12</f>
-        <v>7475984.11796843</v>
+        <v>7418880</v>
       </c>
       <c r="N25" s="14" t="n">
         <f aca="false">(N10-N9*Рычаги!$B$9+N15+N22)*12</f>
-        <v>10224026.4531626</v>
+        <v>10224000</v>
       </c>
       <c r="O25" s="14" t="n">
         <f aca="false">(O10-O9*Рычаги!$B$9+O15+O22)*12</f>
-        <v>13566479.3932007</v>
+        <v>13566640</v>
       </c>
       <c r="P25" s="14" t="n">
         <f aca="false">(P10-P9*Рычаги!$B$9+P15+P22)*12</f>
-        <v>17547087.5069866</v>
+        <v>17499720</v>
       </c>
       <c r="Q25" s="14" t="n">
         <f aca="false">(Q10-Q9*Рычаги!$B$9+Q15+Q22)*12</f>
-        <v>22209330.674651</v>
+        <v>22230480</v>
       </c>
       <c r="R25" s="14" t="n">
         <f aca="false">(R10-R9*Рычаги!$B$9+R15+R22)*12</f>
-        <v>27842489.660599</v>
+        <v>27870240</v>
       </c>
       <c r="S25" s="14" t="n">
         <f aca="false">(S10-S9*Рычаги!$B$9+S15+S22)*12</f>
-        <v>34469737.1076502</v>
+        <v>34626440</v>
       </c>
       <c r="T25" s="14" t="n">
         <f aca="false">(T10-T9*Рычаги!$B$9+T15+T22)*12</f>
-        <v>42115483.953856</v>
+        <v>42344280</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2581,58 +2576,58 @@
       <c r="B27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="E27" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F27" s="15" t="n">
-        <v>38.3333</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>46.6667</v>
-      </c>
-      <c r="H27" s="15" t="n">
+      <c r="F27" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="H27" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="I27" s="15" t="n">
-        <v>61.6667</v>
-      </c>
-      <c r="J27" s="15" t="n">
-        <v>68.3333</v>
-      </c>
-      <c r="K27" s="15" t="n">
+      <c r="I27" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="L27" s="15" t="n">
-        <v>81.6667</v>
-      </c>
-      <c r="M27" s="15" t="n">
-        <v>88.3333</v>
-      </c>
-      <c r="N27" s="15" t="n">
+      <c r="L27" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="N27" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="O27" s="15" t="n">
-        <v>101.6667</v>
-      </c>
-      <c r="P27" s="15" t="n">
-        <v>108.3333</v>
-      </c>
-      <c r="Q27" s="15" t="n">
+      <c r="O27" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="P27" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q27" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="R27" s="15" t="n">
-        <v>121.6667</v>
-      </c>
-      <c r="S27" s="15" t="n">
-        <v>128.3333</v>
-      </c>
-      <c r="T27" s="15" t="n">
+      <c r="R27" s="12" t="n">
+        <v>122</v>
+      </c>
+      <c r="S27" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="T27" s="12" t="n">
         <v>135</v>
       </c>
     </row>
@@ -2657,11 +2652,11 @@
       </c>
       <c r="F28" s="14" t="n">
         <f aca="false">F27*Рычаги!$B$21/12</f>
-        <v>479166.25</v>
+        <v>475000</v>
       </c>
       <c r="G28" s="14" t="n">
         <f aca="false">G27*Рычаги!$B$21/12</f>
-        <v>583333.75</v>
+        <v>587500</v>
       </c>
       <c r="H28" s="14" t="n">
         <f aca="false">H27*Рычаги!$B$21/12</f>
@@ -2669,11 +2664,11 @@
       </c>
       <c r="I28" s="14" t="n">
         <f aca="false">I27*Рычаги!$B$21/12</f>
-        <v>770833.75</v>
+        <v>775000</v>
       </c>
       <c r="J28" s="14" t="n">
         <f aca="false">J27*Рычаги!$B$21/12</f>
-        <v>854166.25</v>
+        <v>850000</v>
       </c>
       <c r="K28" s="14" t="n">
         <f aca="false">K27*Рычаги!$B$21/12</f>
@@ -2681,11 +2676,11 @@
       </c>
       <c r="L28" s="14" t="n">
         <f aca="false">L27*Рычаги!$B$21/12</f>
-        <v>1020833.75</v>
+        <v>1025000</v>
       </c>
       <c r="M28" s="14" t="n">
         <f aca="false">M27*Рычаги!$B$21/12</f>
-        <v>1104166.25</v>
+        <v>1100000</v>
       </c>
       <c r="N28" s="14" t="n">
         <f aca="false">N27*Рычаги!$B$21/12</f>
@@ -2693,11 +2688,11 @@
       </c>
       <c r="O28" s="14" t="n">
         <f aca="false">O27*Рычаги!$B$21/12</f>
-        <v>1270833.75</v>
+        <v>1275000</v>
       </c>
       <c r="P28" s="14" t="n">
         <f aca="false">P27*Рычаги!$B$21/12</f>
-        <v>1354166.25</v>
+        <v>1350000</v>
       </c>
       <c r="Q28" s="14" t="n">
         <f aca="false">Q27*Рычаги!$B$21/12</f>
@@ -2705,11 +2700,11 @@
       </c>
       <c r="R28" s="14" t="n">
         <f aca="false">R27*Рычаги!$B$21/12</f>
-        <v>1520833.75</v>
+        <v>1525000</v>
       </c>
       <c r="S28" s="14" t="n">
         <f aca="false">S27*Рычаги!$B$21/12</f>
-        <v>1604166.25</v>
+        <v>1600000</v>
       </c>
       <c r="T28" s="14" t="n">
         <f aca="false">T27*Рычаги!$B$21/12</f>
@@ -2723,58 +2718,58 @@
       <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="18" t="n">
-        <v>803833.3333</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>1236666.6667</v>
-      </c>
-      <c r="E29" s="18" t="n">
+      <c r="C29" s="17" t="n">
+        <v>803833.33</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>1236666.67</v>
+      </c>
+      <c r="E29" s="17" t="n">
         <v>1669500</v>
       </c>
-      <c r="F29" s="18" t="n">
+      <c r="F29" s="17" t="n">
         <v>1669500</v>
       </c>
-      <c r="G29" s="18" t="n">
+      <c r="G29" s="17" t="n">
         <v>1900000</v>
       </c>
-      <c r="H29" s="18" t="n">
+      <c r="H29" s="17" t="n">
         <v>2130500</v>
       </c>
-      <c r="I29" s="18" t="n">
+      <c r="I29" s="17" t="n">
         <v>2130500</v>
       </c>
-      <c r="J29" s="18" t="n">
-        <v>2224966.6667</v>
-      </c>
-      <c r="K29" s="18" t="n">
-        <v>2319433.3333</v>
-      </c>
-      <c r="L29" s="18" t="n">
+      <c r="J29" s="17" t="n">
+        <v>2224966.67</v>
+      </c>
+      <c r="K29" s="17" t="n">
+        <v>2319433.33</v>
+      </c>
+      <c r="L29" s="17" t="n">
         <v>2413900</v>
       </c>
-      <c r="M29" s="18" t="n">
-        <v>2508366.6667</v>
-      </c>
-      <c r="N29" s="18" t="n">
-        <v>2602833.3333</v>
-      </c>
-      <c r="O29" s="18" t="n">
-        <v>2602833.3333</v>
-      </c>
-      <c r="P29" s="18" t="n">
-        <v>2788366.6667</v>
-      </c>
-      <c r="Q29" s="18" t="n">
+      <c r="M29" s="17" t="n">
+        <v>2508366.67</v>
+      </c>
+      <c r="N29" s="17" t="n">
+        <v>2602833.33</v>
+      </c>
+      <c r="O29" s="17" t="n">
+        <v>2602833.33</v>
+      </c>
+      <c r="P29" s="17" t="n">
+        <v>2788366.67</v>
+      </c>
+      <c r="Q29" s="17" t="n">
         <v>2973900</v>
       </c>
-      <c r="R29" s="18" t="n">
-        <v>3159433.3333</v>
-      </c>
-      <c r="S29" s="18" t="n">
-        <v>3344966.6667</v>
-      </c>
-      <c r="T29" s="18" t="n">
+      <c r="R29" s="17" t="n">
+        <v>3159433.33</v>
+      </c>
+      <c r="S29" s="17" t="n">
+        <v>3344966.67</v>
+      </c>
+      <c r="T29" s="17" t="n">
         <v>3530500</v>
       </c>
     </row>
@@ -2787,11 +2782,11 @@
       </c>
       <c r="C30" s="14" t="n">
         <f aca="false">C29-C28</f>
-        <v>678833.3333</v>
+        <v>678833.33</v>
       </c>
       <c r="D30" s="14" t="n">
         <f aca="false">D29-D28</f>
-        <v>986666.6667</v>
+        <v>986666.67</v>
       </c>
       <c r="E30" s="14" t="n">
         <f aca="false">E29-E28</f>
@@ -2799,11 +2794,11 @@
       </c>
       <c r="F30" s="14" t="n">
         <f aca="false">F29-F28</f>
-        <v>1190333.75</v>
+        <v>1194500</v>
       </c>
       <c r="G30" s="14" t="n">
         <f aca="false">G29-G28</f>
-        <v>1316666.25</v>
+        <v>1312500</v>
       </c>
       <c r="H30" s="14" t="n">
         <f aca="false">H29-H28</f>
@@ -2811,35 +2806,35 @@
       </c>
       <c r="I30" s="14" t="n">
         <f aca="false">I29-I28</f>
-        <v>1359666.25</v>
+        <v>1355500</v>
       </c>
       <c r="J30" s="14" t="n">
         <f aca="false">J29-J28</f>
-        <v>1370800.4167</v>
+        <v>1374966.67</v>
       </c>
       <c r="K30" s="14" t="n">
         <f aca="false">K29-K28</f>
-        <v>1381933.3333</v>
+        <v>1381933.33</v>
       </c>
       <c r="L30" s="14" t="n">
         <f aca="false">L29-L28</f>
-        <v>1393066.25</v>
+        <v>1388900</v>
       </c>
       <c r="M30" s="14" t="n">
         <f aca="false">M29-M28</f>
-        <v>1404200.4167</v>
+        <v>1408366.67</v>
       </c>
       <c r="N30" s="14" t="n">
         <f aca="false">N29-N28</f>
-        <v>1415333.3333</v>
+        <v>1415333.33</v>
       </c>
       <c r="O30" s="14" t="n">
         <f aca="false">O29-O28</f>
-        <v>1331999.5833</v>
+        <v>1327833.33</v>
       </c>
       <c r="P30" s="14" t="n">
         <f aca="false">P29-P28</f>
-        <v>1434200.4167</v>
+        <v>1438366.67</v>
       </c>
       <c r="Q30" s="14" t="n">
         <f aca="false">Q29-Q28</f>
@@ -2847,11 +2842,11 @@
       </c>
       <c r="R30" s="14" t="n">
         <f aca="false">R29-R28</f>
-        <v>1638599.5833</v>
+        <v>1634433.33</v>
       </c>
       <c r="S30" s="14" t="n">
         <f aca="false">S29-S28</f>
-        <v>1740800.4167</v>
+        <v>1744966.67</v>
       </c>
       <c r="T30" s="14" t="n">
         <f aca="false">T29-T28</f>
@@ -2859,7 +2854,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="15" t="s">
         <v>69</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -2867,11 +2862,11 @@
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">C24-C29</f>
-        <v>-803833.3333</v>
+        <v>-803833.33</v>
       </c>
       <c r="D31" s="14" t="n">
         <f aca="false">D24-D29</f>
-        <v>-1232666.6667</v>
+        <v>-1232666.67</v>
       </c>
       <c r="E31" s="14" t="n">
         <f aca="false">E24-E29</f>
@@ -2879,67 +2874,67 @@
       </c>
       <c r="F31" s="14" t="n">
         <f aca="false">F24-F29</f>
-        <v>-1606611.512</v>
+        <v>-1606220</v>
       </c>
       <c r="G31" s="14" t="n">
         <f aca="false">G24-G29</f>
-        <v>-1831783.70544</v>
+        <v>-1831440</v>
       </c>
       <c r="H31" s="14" t="n">
         <f aca="false">H24-H29</f>
-        <v>-2019189.2824466</v>
+        <v>-2012820</v>
       </c>
       <c r="I31" s="14" t="n">
         <f aca="false">I24-I29</f>
-        <v>-1918439.99099444</v>
+        <v>-1913880</v>
       </c>
       <c r="J31" s="14" t="n">
         <f aca="false">J24-J29</f>
-        <v>-1890907.4455744</v>
+        <v>-1890566.67</v>
       </c>
       <c r="K31" s="14" t="n">
         <f aca="false">K24-K29</f>
-        <v>-1827883.60732589</v>
+        <v>-1835883.33</v>
       </c>
       <c r="L31" s="14" t="n">
         <f aca="false">L24-L29</f>
-        <v>-1776875.30736042</v>
+        <v>-1786896.66666667</v>
       </c>
       <c r="M31" s="14" t="n">
         <f aca="false">M24-M29</f>
-        <v>-1685367.99020263</v>
+        <v>-1690126.67</v>
       </c>
       <c r="N31" s="14" t="n">
         <f aca="false">N24-N29</f>
-        <v>-1550831.12886979</v>
+        <v>-1550833.33</v>
       </c>
       <c r="O31" s="14" t="n">
         <f aca="false">O24-O29</f>
-        <v>-1238958.38386661</v>
+        <v>-1222279.99666667</v>
       </c>
       <c r="P31" s="14" t="n">
         <f aca="false">P24-P29</f>
-        <v>-1059444.37445112</v>
+        <v>-1080056.67</v>
       </c>
       <c r="Q31" s="14" t="n">
         <f aca="false">Q24-Q29</f>
-        <v>-823122.44377908</v>
+        <v>-821360</v>
       </c>
       <c r="R31" s="14" t="n">
         <f aca="false">R24-R29</f>
-        <v>-505890.861583414</v>
+        <v>-486913.33</v>
       </c>
       <c r="S31" s="14" t="n">
         <f aca="false">S24-S29</f>
-        <v>-105823.574395817</v>
+        <v>-109430.003333333</v>
       </c>
       <c r="T31" s="14" t="n">
         <f aca="false">T24-T29</f>
-        <v>379123.662821335</v>
+        <v>398190</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="15" t="s">
         <v>70</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -2947,7 +2942,7 @@
       </c>
       <c r="C32" s="14" t="n">
         <f aca="false">Рычаги!$B$23+C31</f>
-        <v>49196166.6667</v>
+        <v>49196166.67</v>
       </c>
       <c r="D32" s="14" t="n">
         <f aca="false">C32+D31</f>
@@ -2959,67 +2954,67 @@
       </c>
       <c r="F32" s="14" t="n">
         <f aca="false">E32+F31</f>
-        <v>44746988.488</v>
+        <v>44747380</v>
       </c>
       <c r="G32" s="14" t="n">
         <f aca="false">F32+G31</f>
-        <v>42915204.78256</v>
+        <v>42915940</v>
       </c>
       <c r="H32" s="14" t="n">
         <f aca="false">G32+H31</f>
-        <v>40896015.5001134</v>
+        <v>40903120</v>
       </c>
       <c r="I32" s="14" t="n">
         <f aca="false">H32+I31</f>
-        <v>38977575.509119</v>
+        <v>38989240</v>
       </c>
       <c r="J32" s="14" t="n">
         <f aca="false">I32+J31</f>
-        <v>37086668.0635446</v>
+        <v>37098673.33</v>
       </c>
       <c r="K32" s="14" t="n">
         <f aca="false">J32+K31</f>
-        <v>35258784.4562187</v>
+        <v>35262790</v>
       </c>
       <c r="L32" s="14" t="n">
         <f aca="false">K32+L31</f>
-        <v>33481909.1488582</v>
+        <v>33475893.3333333</v>
       </c>
       <c r="M32" s="14" t="n">
         <f aca="false">L32+M31</f>
-        <v>31796541.1586556</v>
+        <v>31785766.6633333</v>
       </c>
       <c r="N32" s="14" t="n">
         <f aca="false">M32+N31</f>
-        <v>30245710.0297858</v>
+        <v>30234933.3333333</v>
       </c>
       <c r="O32" s="14" t="n">
         <f aca="false">N32+O31</f>
-        <v>29006751.6459192</v>
+        <v>29012653.3366667</v>
       </c>
       <c r="P32" s="14" t="n">
         <f aca="false">O32+P31</f>
-        <v>27947307.2714681</v>
+        <v>27932596.6666667</v>
       </c>
       <c r="Q32" s="14" t="n">
         <f aca="false">P32+Q31</f>
-        <v>27124184.827689</v>
+        <v>27111236.6666667</v>
       </c>
       <c r="R32" s="14" t="n">
         <f aca="false">Q32+R31</f>
-        <v>26618293.9661056</v>
+        <v>26624323.3366667</v>
       </c>
       <c r="S32" s="14" t="n">
         <f aca="false">R32+S31</f>
-        <v>26512470.3917098</v>
+        <v>26514893.3333333</v>
       </c>
       <c r="T32" s="14" t="n">
         <f aca="false">S32+T31</f>
-        <v>26891594.0545311</v>
+        <v>26913083.3333333</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="15" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3119,225 +3114,225 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>82</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>42000000</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="19" t="n">
         <f aca="false">Модель!T25</f>
-        <v>42115483.953856</v>
-      </c>
-      <c r="D5" s="21" t="str">
+        <v>42344280</v>
+      </c>
+      <c r="D5" s="20" t="str">
         <f aca="false">IF(ABS(C5-B5)&lt;=1500000,"да","НЕТ")</f>
         <v>да</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>83</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>3600000</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="19" t="n">
         <f aca="false">Модель!T24-Модель!T17</f>
-        <v>3509623.66282134</v>
-      </c>
-      <c r="D6" s="21" t="str">
+        <v>3528690</v>
+      </c>
+      <c r="D6" s="20" t="str">
         <f aca="false">IF(ABS(C6-B6)&lt;=300000,"да","НЕТ")</f>
         <v>да</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>84</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>3600000</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <f aca="false">Модель!T24</f>
-        <v>3909623.66282134</v>
-      </c>
-      <c r="D7" s="21" t="str">
+        <v>3928690</v>
+      </c>
+      <c r="D7" s="20" t="str">
         <f aca="false">IF(ABS(C7-B7)&lt;=300000,"да","НЕТ")</f>
         <v>НЕТ</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>85</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>4000000</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <f aca="false">Модель!T29</f>
         <v>3530500</v>
       </c>
-      <c r="D8" s="21" t="str">
+      <c r="D8" s="20" t="str">
         <f aca="false">IF(ABS(C8-B8)&lt;=300000,"да","НЕТ")</f>
         <v>НЕТ</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>86</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>-350000</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <f aca="false">Модель!T31</f>
-        <v>379123.662821335</v>
-      </c>
-      <c r="D9" s="21" t="str">
+        <v>398190</v>
+      </c>
+      <c r="D9" s="20" t="str">
         <f aca="false">IF(ABS(C9-B9)&lt;=300000,"да","НЕТ")</f>
         <v>НЕТ</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>87</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>21000000</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <f aca="false">Модель!T32</f>
-        <v>26891594.0545311</v>
-      </c>
-      <c r="D10" s="21" t="str">
+        <v>26913083.3333333</v>
+      </c>
+      <c r="D10" s="20" t="str">
         <f aca="false">IF(ABS(C10-B10)&lt;=2000000,"да","НЕТ")</f>
         <v>НЕТ</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>88</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="21" t="n">
         <f aca="false">Модель!H7</f>
-        <v>8.67671358</v>
-      </c>
-      <c r="D11" s="21" t="str">
+        <v>10</v>
+      </c>
+      <c r="D11" s="20" t="str">
         <f aca="false">IF(C11&gt;=B11*0.85,"да","НЕТ")</f>
         <v>да</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>89</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="21" t="n">
         <f aca="false">Модель!Q7</f>
-        <v>102.799487817802</v>
-      </c>
-      <c r="D12" s="21" t="str">
+        <v>103</v>
+      </c>
+      <c r="D12" s="20" t="str">
         <f aca="false">IF(C12&gt;=B12*0.85,"да","НЕТ")</f>
         <v>да</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>90</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>157</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="21" t="n">
         <f aca="false">Модель!T7</f>
-        <v>157.693040230126</v>
-      </c>
-      <c r="D13" s="21" t="str">
+        <v>159</v>
+      </c>
+      <c r="D13" s="20" t="str">
         <f aca="false">IF(ABS(C13-B13)&lt;=5,"да","НЕТ")</f>
         <v>да</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>91</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="21" t="n">
         <f aca="false">Модель!H20</f>
-        <v>17.2376438975</v>
-      </c>
-      <c r="D14" s="21" t="str">
+        <v>17</v>
+      </c>
+      <c r="D14" s="20" t="str">
         <f aca="false">IF(C14&gt;=B14*0.85,"да","НЕТ")</f>
         <v>да</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>92</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>170</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="21" t="n">
         <f aca="false">Модель!Q20</f>
-        <v>179.422703690869</v>
-      </c>
-      <c r="D15" s="21" t="str">
+        <v>179</v>
+      </c>
+      <c r="D15" s="20" t="str">
         <f aca="false">IF(C15&gt;=B15*0.85,"да","НЕТ")</f>
         <v>да</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>93</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>256</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="21" t="n">
         <f aca="false">Модель!T20</f>
-        <v>292.264936305647</v>
-      </c>
-      <c r="D16" s="21" t="str">
+        <v>292</v>
+      </c>
+      <c r="D16" s="20" t="str">
         <f aca="false">IF(ABS(C16-B16)&lt;=10,"да","НЕТ")</f>
         <v>НЕТ</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>94</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>63500</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="21" t="n">
         <f aca="false">Модель!T14</f>
-        <v>55969.8186758158</v>
-      </c>
-      <c r="D17" s="21" t="str">
+        <v>55969</v>
+      </c>
+      <c r="D17" s="20" t="str">
         <f aca="false">IF(ABS(C17-B17)&lt;=2000,"да","НЕТ")</f>
         <v>НЕТ</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>95</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>135</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="21" t="n">
         <f aca="false">Модель!T27</f>
         <v>135</v>
       </c>
-      <c r="D18" s="21" t="str">
+      <c r="D18" s="20" t="str">
         <f aca="false">IF(ABS(C18-B18)&lt;=5,"да","НЕТ")</f>
         <v>да</v>
       </c>
